--- a/output/voter_output.xlsx
+++ b/output/voter_output.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H892"/>
+  <dimension ref="A1:H890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -625,11 +625,7 @@
           <t>GNANAPRAKASSH</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>JAYASANKAR</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Other</t>
@@ -675,11 +671,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>2FF2, 1st floor</t>
-        </is>
-      </c>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -778,16 +770,15 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>THAIYALNAYAGI ALIAS KUMARI</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>PALANI ALIAS
 PALANIVEL Photo</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>PALANI ALIAS
-PALANIVEL Photo</t>
-        </is>
-      </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -798,11 +789,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -833,11 +820,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>48</t>
@@ -949,11 +932,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -976,7 +955,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>AROKIASAMY</t>
+          <t>JOSEPH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1221,11 +1200,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>40</t>
@@ -1243,7 +1218,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>IPD0090993</t>
+          <t>IPO0090993</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1288,7 +1263,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>SVVANANDHAN</t>
+          <t>SIVANANDHAN</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1381,12 +1356,12 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -1442,16 +1417,8 @@
           <t>IPO0100693</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Manohar</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Subaramaniyan</t>
-        </is>
-      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -1559,22 +1526,22 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>UIJ0046300</t>
+          <t>IPD0100701</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>JAYARAJ</t>
+          <t>Manohar</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>ISSAC</t>
+          <t>Manohar</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1582,14 +1549,10 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1599,22 +1562,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>IPD0100701</t>
+          <t>UIJ0046300</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Gokila</t>
+          <t>JAYARAJ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Manohar</t>
+          <t>ISSAC</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1622,14 +1585,10 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1702,11 +1661,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -1742,11 +1697,7 @@
           <t>8A</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+      <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -1807,11 +1758,7 @@
           <t>SANTHAKUMARI</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>KARUNANIDHI</t>
-        </is>
-      </c>
+      <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -1839,7 +1786,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>IPO0040618</t>
+          <t>IPD0040618</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2164,7 +2111,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Vignesh</t>
+          <t>Revathi</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -2207,11 +2154,7 @@
           <t>Vijayakumar</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>Kumar</t>
-        </is>
-      </c>
+      <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -2219,7 +2162,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2297,11 +2240,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
           <t>60</t>
@@ -2337,12 +2276,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -2435,19 +2374,11 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>IPO0126706</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>LAKSHMANAN</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>LAKSHMANAN</t>
-        </is>
-      </c>
+          <t>IPD0126706</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -2475,7 +2406,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>IPO0190314</t>
+          <t>IPD0190314</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -2573,11 +2504,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -2636,7 +2563,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>JAYA AROKIA JENIFER</t>
+          <t>JOSEPH</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2694,7 +2621,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -2735,7 +2666,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -2743,22 +2678,22 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>IPD0100750</t>
+          <t>IPD0100743</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Mangalam</t>
+          <t>SUNDARARAMAN</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>SUNDARARAMAN</t>
+          <t>BALASUBRAMANIAN</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2768,12 +2703,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2783,22 +2718,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>IPD0100743</t>
+          <t>IPD0100750</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
+          <t>Mangalam</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
           <t>SUNDARARAMAN</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>BALASUBRAMANIAN</t>
-        </is>
-      </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2808,12 +2743,12 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2758,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ZHN0003753</t>
+          <t>ZHN0037531</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2944,7 +2879,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>MADALAI MUTHU</t>
+          <t>ARUL SAMY</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -3007,11 +2942,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -3104,14 +3035,10 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>MATHALAIMUTHU</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>MATHALAIMUTHU</t>
-        </is>
-      </c>
+          <t>NOVA SELIN</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -3167,7 +3094,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -3180,7 +3111,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>PAULRAJ</t>
+          <t>JEAN GERARD RAJI</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -3234,11 +3165,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
+      <c r="G72" s="3" t="inlineStr"/>
       <c r="H72" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3269,16 +3196,8 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="F73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3314,7 +3233,11 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -3327,7 +3250,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>IPD0100776</t>
+          <t>IIP0010077</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -3390,11 +3313,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3412,7 +3331,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>SATHIYA</t>
+          <t>MUNUSAMY</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -3465,11 +3384,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3501,7 +3416,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -3559,19 +3478,11 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>IPO0069161</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>DHAKSHINAMOORTHY</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>DHAKSHINAMOORTHY</t>
-        </is>
-      </c>
+          <t>IPD0069161</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr"/>
+      <c r="D81" s="3" t="inlineStr"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -3599,7 +3510,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>IPO0084681</t>
+          <t>IPD0084681</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -3607,11 +3518,7 @@
           <t>PRIYANKA</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>DHASHINAMURTHY</t>
-        </is>
-      </c>
+      <c r="D82" s="3" t="inlineStr"/>
       <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -3639,7 +3546,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>IPO0095497</t>
+          <t>IPD0095497</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -3697,11 +3604,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+      <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3724,7 +3627,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>KALAIYARASI</t>
+          <t>MOORTHY</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -3795,12 +3698,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>IPD0046381</t>
+          <t>IPD0046581</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>RAJAKUMARAN</t>
+          <t>MOORTHY</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -3875,7 +3778,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>IPD0100818</t>
+          <t>IPO0100818</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3915,22 +3818,18 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>CMS0273201</t>
+          <t>GKY0562256</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>Lakshmi</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Krishnamoorthy</t>
-        </is>
-      </c>
+          <t>SUMATHI</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3940,7 +3839,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
@@ -3955,18 +3854,22 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>GKY0562256</t>
+          <t>CMS0273201</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>SUMATHI</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr"/>
+          <t>Krishnamoorthy</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Krishnamoorthy</t>
+        </is>
+      </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3974,11 +3877,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="G91" s="3" t="inlineStr"/>
       <c r="H91" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -4054,11 +3953,7 @@
           <t>194</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="G93" s="3" t="inlineStr"/>
       <c r="H93" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -4091,14 +3986,10 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr"/>
       <c r="H94" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -4131,7 +4022,7 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>194,</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -4159,7 +4050,11 @@
           <t>PITCHE</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr"/>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>SOUPRAMANIEN</t>
+        </is>
+      </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -4272,7 +4167,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>BALAKUMAR</t>
+          <t>SHARMILA</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -4335,7 +4230,11 @@
           <t>85</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
@@ -4366,11 +4265,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="G101" s="3" t="inlineStr"/>
       <c r="H101" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -4403,7 +4298,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -4441,11 +4336,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" s="3" t="inlineStr">
         <is>
           <t>58</t>
@@ -4481,17 +4372,17 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
@@ -4519,7 +4410,7 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -4637,7 +4528,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
           <t>63</t>
@@ -4673,7 +4568,11 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr"/>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
           <t>59</t>
@@ -4734,16 +4633,8 @@
           <t>GKY0699215</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>Pavadai</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Pavadai</t>
-        </is>
-      </c>
+      <c r="C111" s="3" t="inlineStr"/>
+      <c r="D111" s="3" t="inlineStr"/>
       <c r="E111" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -4771,7 +4662,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>IPO0100909</t>
+          <t>IPD0100909</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -4816,7 +4707,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Thaiyalnayagi Tamilvani</t>
+          <t>Thalyainayagi Tamilvani</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -4909,11 +4800,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="F115" s="3" t="inlineStr"/>
       <c r="G115" s="3" t="inlineStr"/>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -4945,11 +4832,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" s="3" t="inlineStr">
         <is>
           <t>48</t>
@@ -4967,7 +4850,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>IPO0095158</t>
+          <t>IPO0009515</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -5025,11 +4908,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="F118" s="3" t="inlineStr"/>
       <c r="G118" s="3" t="inlineStr">
         <is>
           <t>34</t>
@@ -5075,7 +4954,11 @@
           <t>29</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
@@ -5083,17 +4966,17 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>IPD0127738</t>
+          <t>IPD0080937</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>ACHUTHAN</t>
+          <t>KIRUBAVATHI</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>SAYIRAM</t>
+          <t>SENTHILVEL</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -5109,7 +4992,7 @@
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5119,17 +5002,17 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>IPD0080937</t>
+          <t>IPD0127738</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>KIRUBAVATHI</t>
+          <t>ACHUTHAN</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>SENTHILVEL</t>
+          <t>SAYIRAM</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -5149,7 +5032,7 @@
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5287,11 +5170,7 @@
           <t>Bakkiyalakshmi</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>Thirumalavan</t>
-        </is>
-      </c>
+      <c r="D125" s="3" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -5327,7 +5206,11 @@
           <t>LAKSHMANAN</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr"/>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>GOPALAKRISHNAN</t>
+        </is>
+      </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -5355,7 +5238,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>IPO0198374</t>
+          <t>IPD0198374</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -5373,11 +5256,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+      <c r="F127" s="3" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5555,7 +5434,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>JTP0056320</t>
+          <t>JTP0563205</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -5575,7 +5454,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>38A</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -5676,7 +5555,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>MEENATCHI</t>
+          <t>SAKTHIVEL</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -5691,7 +5570,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>NO:2, GAYATHRI HOMES</t>
+          <t>NO:2, GAYATHRI HOMES.</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -5734,11 +5613,7 @@
           <t>No:2,Gayathri Homes,3rd</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="G136" s="3" t="inlineStr"/>
       <c r="H136" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -5756,7 +5631,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>KARUPPIAH</t>
+          <t>RAJAMMAL</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -5907,10 +5782,14 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>IPD0200576</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr"/>
+          <t>IPO0200576</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>Neela</t>
+        </is>
+      </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
           <t>VENKATASUBRAMANIAN</t>
@@ -5948,7 +5827,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>M ANNACATTY</t>
+          <t>KRISHNAN</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
@@ -5966,11 +5845,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
+      <c r="G142" s="3" t="inlineStr"/>
       <c r="H142" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -6001,7 +5876,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr"/>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
           <t>65</t>
@@ -6024,7 +5903,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>VIUAYAKUMARI</t>
+          <t>VIJAYAKUMARI</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
@@ -6084,7 +5963,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
@@ -6167,7 +6046,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr"/>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
@@ -6180,7 +6063,7 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>KANNAIYAN</t>
+          <t>CHITRA</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
@@ -6223,11 +6106,7 @@
           <t>MANJULA</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>KUMAR</t>
-        </is>
-      </c>
+      <c r="D149" s="3" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -6313,11 +6192,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr">
         <is>
           <t>53</t>
@@ -6354,11 +6229,7 @@
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr"/>
-      <c r="G152" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="G152" s="3" t="inlineStr"/>
       <c r="H152" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -6389,11 +6260,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
+      <c r="F153" s="3" t="inlineStr"/>
       <c r="G153" s="3" t="inlineStr">
         <is>
           <t>50</t>
@@ -6652,14 +6519,14 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
+          <t>Ramesh</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
           <t>Rajaraman</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>Rajaraman</t>
-        </is>
-      </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -6675,11 +6542,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+      <c r="H160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
@@ -6687,7 +6550,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>IPO0035725</t>
+          <t>IIP0003572</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -6705,7 +6568,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr"/>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
           <t>38</t>
@@ -6723,7 +6590,7 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>IPO0004037</t>
+          <t>IPD0040378</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -6781,11 +6648,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F163" s="3" t="inlineStr"/>
       <c r="G163" s="3" t="inlineStr">
         <is>
           <t>32</t>
@@ -6808,7 +6671,7 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>IYYAPPAN</t>
+          <t>PAZHANIVEL</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -6879,12 +6742,12 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>IPO0069991</t>
+          <t>IPO0069591</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>DHIVAGAR</t>
+          <t>JAYAVADIVEL</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
@@ -6924,7 +6787,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Jayakumar</t>
+          <t>Manjusri</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
@@ -6982,11 +6845,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G168" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="G168" s="3" t="inlineStr"/>
       <c r="H168" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -6999,17 +6858,17 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>IPD0102657</t>
+          <t>GKY0383067</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>RAJALAKSHMI</t>
+          <t>RATHI</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>RAJARAMAN</t>
+          <t>RAJARAM</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -7022,11 +6881,7 @@
           <t>1A</t>
         </is>
       </c>
-      <c r="G169" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="G169" s="3" t="inlineStr"/>
       <c r="H169" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -7039,17 +6894,17 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>GKY0383067</t>
+          <t>IPD0102657</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>RATHI</t>
+          <t>RAJALAKSHMI</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>RAJARAM</t>
+          <t>RAJARAMAN</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -7062,11 +6917,7 @@
           <t>1A</t>
         </is>
       </c>
-      <c r="G170" s="3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+      <c r="G170" s="3" t="inlineStr"/>
       <c r="H170" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -7084,7 +6935,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>Arumugam</t>
+          <t>Vaithyalingam</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -7182,11 +7033,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
+      <c r="G173" s="3" t="inlineStr"/>
       <c r="H173" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -7327,21 +7174,13 @@
           <t>SHRINE DEVA ANAND</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>BABU RAO</t>
-        </is>
-      </c>
+      <c r="D177" s="3" t="inlineStr"/>
       <c r="E177" s="3" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="F177" s="3" t="inlineStr"/>
       <c r="G177" s="3" t="inlineStr">
         <is>
           <t>34</t>
@@ -7407,11 +7246,7 @@
           <t>Manuel</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Arulanand</t>
-        </is>
-      </c>
+      <c r="D179" s="3" t="inlineStr"/>
       <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -7537,16 +7372,8 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="F182" s="3" t="inlineStr"/>
+      <c r="G182" s="3" t="inlineStr"/>
       <c r="H182" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -7577,11 +7404,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
+      <c r="F183" s="3" t="inlineStr"/>
       <c r="G183" s="3" t="inlineStr">
         <is>
           <t>45</t>
@@ -7659,7 +7482,7 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -7773,7 +7596,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F188" s="3" t="inlineStr"/>
+      <c r="F188" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
           <t>40</t>
@@ -7889,11 +7716,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="F191" s="3" t="inlineStr"/>
       <c r="G191" s="3" t="inlineStr">
         <is>
           <t>32</t>
@@ -7911,7 +7734,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>IPD0230896</t>
+          <t>IPD0023089</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -7969,11 +7792,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="F193" s="3" t="inlineStr"/>
       <c r="G193" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -8009,12 +7828,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="inlineStr"/>
+      <c r="F194" s="3" t="inlineStr"/>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -8107,7 +7926,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>IPO0006163</t>
+          <t>IPD0006163</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -8165,11 +7984,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="F198" s="3" t="inlineStr"/>
       <c r="G198" s="3" t="inlineStr">
         <is>
           <t>34</t>
@@ -8187,34 +8002,30 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>IPD0013847</t>
+          <t>IPD0035659</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>MATCHAGANDHI</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>VEERAPPAN</t>
+          <t>KUMAR</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr"/>
       <c r="H199" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8227,34 +8038,30 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>IPD0035659</t>
+          <t>IPD0013847</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MATCHAGANDHI</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>KUMAR</t>
+          <t>VEERAPPAN</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr"/>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8370,11 +8177,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+      <c r="G203" s="3" t="inlineStr"/>
       <c r="H203" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8405,11 +8208,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="F204" s="3" t="inlineStr"/>
       <c r="G204" s="3" t="inlineStr">
         <is>
           <t>62</t>
@@ -8467,7 +8266,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>IPD0103034</t>
+          <t>IPD0103036</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -8485,11 +8284,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="F206" s="3" t="inlineStr"/>
       <c r="G206" s="3" t="inlineStr">
         <is>
           <t>52</t>
@@ -8535,7 +8330,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="H207" s="3" t="inlineStr"/>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n">
@@ -8603,7 +8402,11 @@
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr"/>
-      <c r="G209" s="3" t="inlineStr"/>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8656,7 +8459,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>ZHN0008896</t>
+          <t>ZHN0000889</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -8664,11 +8467,7 @@
           <t>RUBINA BANU</t>
         </is>
       </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>MOHAMED SHAMIR</t>
-        </is>
-      </c>
+      <c r="D211" s="3" t="inlineStr"/>
       <c r="E211" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -8714,11 +8513,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="F212" s="3" t="inlineStr"/>
       <c r="G212" s="3" t="inlineStr"/>
       <c r="H212" s="3" t="inlineStr">
         <is>
@@ -8735,16 +8530,8 @@
           <t>XYA0756692</t>
         </is>
       </c>
-      <c r="C213" s="3" t="inlineStr">
-        <is>
-          <t>SATHISHKUMAR</t>
-        </is>
-      </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>SATHISHKUMAR</t>
-        </is>
-      </c>
+      <c r="C213" s="3" t="inlineStr"/>
+      <c r="D213" s="3" t="inlineStr"/>
       <c r="E213" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -8817,7 +8604,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>ELANGOVAN</t>
+          <t>SIVAKAMY</t>
         </is>
       </c>
       <c r="D215" s="3" t="inlineStr">
@@ -8870,7 +8657,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F216" s="3" t="inlineStr"/>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -8913,7 +8704,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
@@ -8947,7 +8738,11 @@
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr"/>
-      <c r="G218" s="3" t="inlineStr"/>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -9018,21 +8813,13 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="F220" s="3" t="inlineStr"/>
       <c r="G220" s="3" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="H220" s="3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+      <c r="H220" s="3" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n">
@@ -9125,7 +8912,7 @@
       </c>
       <c r="C223" s="3" t="inlineStr">
         <is>
-          <t>SAVITHAI</t>
+          <t>SAVITHRI</t>
         </is>
       </c>
       <c r="D223" s="3" t="inlineStr">
@@ -9138,11 +8925,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="F223" s="3" t="inlineStr"/>
       <c r="G223" s="3" t="inlineStr">
         <is>
           <t>72</t>
@@ -9178,11 +8961,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="F224" s="3" t="inlineStr"/>
       <c r="G224" s="3" t="inlineStr"/>
       <c r="H224" s="3" t="inlineStr">
         <is>
@@ -9344,7 +9123,11 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H228" s="3" t="inlineStr"/>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n">
@@ -9352,22 +9135,22 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>IPD0091215</t>
+          <t>NZJ0802587</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
         <is>
-          <t>PHRABU</t>
+          <t>GAYATHRI</t>
         </is>
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>SRINIVASAN</t>
+          <t>VISVANATHAN</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -9375,14 +9158,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="G229" s="3" t="inlineStr"/>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9392,22 +9171,22 @@
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>NZJ0802587</t>
+          <t>IPD0091215</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
         <is>
-          <t>GAYATHRI</t>
+          <t>PHRABU</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>VISVANATHAN</t>
+          <t>SRINIVASAN</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -9415,14 +9194,10 @@
           <t>7</t>
         </is>
       </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="G230" s="3" t="inlineStr"/>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9207,7 @@
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>SCC0110184</t>
+          <t>SCO0101865</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -9517,7 +9292,7 @@
       </c>
       <c r="C233" s="3" t="inlineStr">
         <is>
-          <t>SARANYA</t>
+          <t>GOPU</t>
         </is>
       </c>
       <c r="D233" s="3" t="inlineStr">
@@ -9536,7 +9311,11 @@
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr"/>
-      <c r="H233" s="3" t="inlineStr"/>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n">
@@ -9585,7 +9364,7 @@
       </c>
       <c r="C235" s="3" t="inlineStr">
         <is>
-          <t>Manimozhi</t>
+          <t>Parimala</t>
         </is>
       </c>
       <c r="D235" s="3" t="inlineStr">
@@ -9620,7 +9399,7 @@
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>UIJ0113183</t>
+          <t>ULJ0113183</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -9684,7 +9463,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H237" s="3" t="inlineStr"/>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n">
@@ -9697,7 +9480,7 @@
       </c>
       <c r="C238" s="3" t="inlineStr">
         <is>
-          <t>RAJASEKAR</t>
+          <t>RAJU</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
@@ -9755,12 +9538,12 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G239" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H239" s="3" t="inlineStr"/>
+      <c r="G239" s="3" t="inlineStr"/>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n">
@@ -9776,11 +9559,7 @@
           <t>PARAMESWARI</t>
         </is>
       </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>RAMKUMAR</t>
-        </is>
-      </c>
+      <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -9867,11 +9646,7 @@
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="G242" s="3" t="inlineStr"/>
       <c r="H242" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -9892,22 +9667,13 @@
           <t>IRUDHAYARAJ</t>
         </is>
       </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>PUGAZHENDI ALIAS
-AROKIASAMY Photo</t>
-        </is>
-      </c>
+      <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
+      <c r="F243" s="3" t="inlineStr"/>
       <c r="G243" s="3" t="inlineStr">
         <is>
           <t>37</t>
@@ -9930,7 +9696,7 @@
       </c>
       <c r="C244" s="3" t="inlineStr">
         <is>
-          <t>lrudhayaraj</t>
+          <t>ATHISTALAKSHMI</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
@@ -9988,11 +9754,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="G245" s="3" t="inlineStr"/>
       <c r="H245" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10063,7 +9825,11 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F247" s="3" t="inlineStr"/>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
           <t>47</t>
@@ -10099,7 +9865,11 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F248" s="3" t="inlineStr"/>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
           <t>51</t>
@@ -10322,7 +10092,7 @@
       </c>
       <c r="C254" s="3" t="inlineStr">
         <is>
-          <t>KALAIVANI</t>
+          <t>AMIRDHALINGAM</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
@@ -10397,12 +10167,12 @@
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>IPO0069377</t>
+          <t>IPD0069377</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
         <is>
-          <t>THAIYANAYAGI</t>
+          <t>KRISHNAN</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
@@ -10456,11 +10226,7 @@
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr"/>
-      <c r="G257" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+      <c r="G257" s="3" t="inlineStr"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10496,11 +10262,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="G258" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="G258" s="3" t="inlineStr"/>
       <c r="H258" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10513,22 +10275,22 @@
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>IPD0088443</t>
+          <t>LOD0211409</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
         <is>
-          <t>SUGUMAR</t>
+          <t>VANITHA</t>
         </is>
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>BALASUNDRAN</t>
+          <t>LAKSHMANAN</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -10536,14 +10298,10 @@
           <t>11</t>
         </is>
       </c>
-      <c r="G259" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="G259" s="3" t="inlineStr"/>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -10553,22 +10311,22 @@
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>LOD0211409</t>
+          <t>IPD0088443</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
         <is>
-          <t>VANITHA</t>
+          <t>SUGUMAR</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>LAKSHMANAN</t>
+          <t>BALASUNDRAN</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -10578,12 +10336,12 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -10641,19 +10399,27 @@
           <t>HEMA</t>
         </is>
       </c>
-      <c r="D262" s="3" t="inlineStr"/>
-      <c r="E262" s="3" t="inlineStr"/>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>PAZHANIVEL</t>
+        </is>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="G262" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H262" s="3" t="inlineStr"/>
+      <c r="G262" s="3" t="inlineStr"/>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n">
@@ -10729,7 +10495,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="H264" s="3" t="inlineStr"/>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n">
@@ -10745,11 +10515,7 @@
           <t>SAGAYAMARY</t>
         </is>
       </c>
-      <c r="D265" s="3" t="inlineStr">
-        <is>
-          <t>ANANDA SAVARIMUTHU</t>
-        </is>
-      </c>
+      <c r="D265" s="3" t="inlineStr"/>
       <c r="E265" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -10762,7 +10528,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H265" s="3" t="inlineStr">
@@ -11040,11 +10806,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+      <c r="G272" s="3" t="inlineStr"/>
       <c r="H272" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -11185,11 +10947,7 @@
           <t>ARUN DOLPHIN DISOUSA</t>
         </is>
       </c>
-      <c r="D276" s="3" t="inlineStr">
-        <is>
-          <t>ANANDA SAVARIMUTHU</t>
-        </is>
-      </c>
+      <c r="D276" s="3" t="inlineStr"/>
       <c r="E276" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -11225,11 +10983,7 @@
           <t>MARYA ARUL AKASH</t>
         </is>
       </c>
-      <c r="D277" s="3" t="inlineStr">
-        <is>
-          <t>ANANDA SAVARIMUTHU</t>
-        </is>
-      </c>
+      <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -11275,12 +11029,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F278" s="3" t="inlineStr"/>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr"/>
       <c r="H278" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -11338,14 +11092,10 @@
       </c>
       <c r="C280" s="3" t="inlineStr">
         <is>
-          <t>mariappan</t>
-        </is>
-      </c>
-      <c r="D280" s="3" t="inlineStr">
-        <is>
-          <t>mariappan</t>
-        </is>
-      </c>
+          <t>rajasekaran</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -11373,7 +11123,7 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>IPD0010314</t>
+          <t>IPD0103143</t>
         </is>
       </c>
       <c r="C281" s="3" t="inlineStr">
@@ -11381,11 +11131,7 @@
           <t>JAGATHIESAN</t>
         </is>
       </c>
-      <c r="D281" s="3" t="inlineStr">
-        <is>
-          <t>SUBRAMANI</t>
-        </is>
-      </c>
+      <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -11458,7 +11204,7 @@
       </c>
       <c r="C283" s="3" t="inlineStr">
         <is>
-          <t>kaleeswari</t>
+          <t>rajasekaran</t>
         </is>
       </c>
       <c r="D283" s="3" t="inlineStr">
@@ -11471,11 +11217,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F283" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="F283" s="3" t="inlineStr"/>
       <c r="G283" s="3" t="inlineStr">
         <is>
           <t>46</t>
@@ -11573,19 +11315,11 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>IPO0009185</t>
-        </is>
-      </c>
-      <c r="C286" s="3" t="inlineStr">
-        <is>
-          <t>REVATHI</t>
-        </is>
-      </c>
-      <c r="D286" s="3" t="inlineStr">
-        <is>
-          <t>SENTHILRAJAN</t>
-        </is>
-      </c>
+          <t>IPO0091850</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="inlineStr"/>
+      <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -11613,7 +11347,7 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>ULJ0111575</t>
+          <t>UIJ0111575</t>
         </is>
       </c>
       <c r="C287" s="3" t="inlineStr">
@@ -11693,22 +11427,22 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>IPD0205674</t>
+          <t>IPD0196139</t>
         </is>
       </c>
       <c r="C289" s="3" t="inlineStr">
         <is>
-          <t>AJITHKUMAR</t>
+          <t>DIVYA</t>
         </is>
       </c>
       <c r="D289" s="3" t="inlineStr">
         <is>
-          <t>RAJASEKARAN</t>
+          <t>PARUVATHAM</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -11718,12 +11452,12 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H289" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -11733,22 +11467,22 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>IPD0196139</t>
+          <t>IPD0205674</t>
         </is>
       </c>
       <c r="C290" s="3" t="inlineStr">
         <is>
-          <t>DIVYA</t>
+          <t>AJITHKUMAR</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>PARUVATHAM</t>
+          <t>RAJASEKARAN</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -11756,14 +11490,10 @@
           <t>13</t>
         </is>
       </c>
-      <c r="G290" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="G290" s="3" t="inlineStr"/>
       <c r="H290" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -11781,11 +11511,7 @@
           <t>SESUMARY</t>
         </is>
       </c>
-      <c r="D291" s="3" t="inlineStr">
-        <is>
-          <t>JOHN VICTOR</t>
-        </is>
-      </c>
+      <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -11841,7 +11567,11 @@
           <t>53</t>
         </is>
       </c>
-      <c r="H292" s="3" t="inlineStr"/>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n">
@@ -11857,8 +11587,16 @@
           <t>PARTHASARATHY</t>
         </is>
       </c>
-      <c r="D293" s="3" t="inlineStr"/>
-      <c r="E293" s="3" t="inlineStr"/>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>MANI</t>
+        </is>
+      </c>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -11904,7 +11642,11 @@
           <t>14</t>
         </is>
       </c>
-      <c r="G294" s="3" t="inlineStr"/>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="H294" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -11925,11 +11667,7 @@
           <t>LEELAVATHI</t>
         </is>
       </c>
-      <c r="D295" s="3" t="inlineStr">
-        <is>
-          <t>MUTHUKUMAR</t>
-        </is>
-      </c>
+      <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -11997,7 +11735,7 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>IPO0028647</t>
+          <t>IPD0028647</t>
         </is>
       </c>
       <c r="C297" s="3" t="inlineStr">
@@ -12042,14 +11780,14 @@
       </c>
       <c r="C298" s="3" t="inlineStr">
         <is>
+          <t>SUGANYA</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
           <t>LOGANATHAN</t>
         </is>
       </c>
-      <c r="D298" s="3" t="inlineStr">
-        <is>
-          <t>LOGANATHAN</t>
-        </is>
-      </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -12065,7 +11803,11 @@
           <t>33</t>
         </is>
       </c>
-      <c r="H298" s="3" t="inlineStr"/>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n">
@@ -12093,14 +11835,10 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="G299" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+          <t>14B</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr"/>
       <c r="H299" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12133,7 +11871,7 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>14B</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -12173,7 +11911,7 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>14B</t>
+          <t>14B.</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -12271,11 +12009,7 @@
       <c r="A304" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="B304" s="3" t="inlineStr">
-        <is>
-          <t>SCO0185538</t>
-        </is>
-      </c>
+      <c r="B304" s="3" t="inlineStr"/>
       <c r="C304" s="3" t="inlineStr">
         <is>
           <t>POUCHEPA</t>
@@ -12313,7 +12047,7 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>SCO0042556</t>
+          <t>COO0042556</t>
         </is>
       </c>
       <c r="C305" s="3" t="inlineStr">
@@ -12321,11 +12055,7 @@
           <t>BALAJI</t>
         </is>
       </c>
-      <c r="D305" s="3" t="inlineStr">
-        <is>
-          <t>GOBINATHAN</t>
-        </is>
-      </c>
+      <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -12373,7 +12103,7 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>14.¢</t>
+          <t>14 c</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -12413,7 +12143,7 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -12451,12 +12181,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F308" s="3" t="inlineStr"/>
-      <c r="G308" s="3" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+      <c r="F308" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G308" s="3" t="inlineStr"/>
       <c r="H308" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -12514,7 +12244,7 @@
       </c>
       <c r="C310" s="3" t="inlineStr">
         <is>
-          <t>SELVI</t>
+          <t>SUBBURAIYALU</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
@@ -12554,7 +12284,7 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>SELVARAJ</t>
+          <t>NANAVEL</t>
         </is>
       </c>
       <c r="D311" s="3" t="inlineStr">
@@ -12612,11 +12342,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G312" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="G312" s="3" t="inlineStr"/>
       <c r="H312" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12692,7 +12418,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G314" s="3" t="inlineStr"/>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="H314" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12753,11 +12483,7 @@
           <t>VIJAYAKUMAR</t>
         </is>
       </c>
-      <c r="D316" s="3" t="inlineStr">
-        <is>
-          <t>KUBENTHIRAN</t>
-        </is>
-      </c>
+      <c r="D316" s="3" t="inlineStr"/>
       <c r="E316" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -12785,7 +12511,7 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>CXX2237035</t>
+          <t>CXZ3703527</t>
         </is>
       </c>
       <c r="C317" s="3" t="inlineStr">
@@ -12865,19 +12591,15 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>IPD0040766</t>
+          <t>CMS0348987</t>
         </is>
       </c>
       <c r="C319" s="3" t="inlineStr">
         <is>
-          <t>MANIMEGALAI</t>
-        </is>
-      </c>
-      <c r="D319" s="3" t="inlineStr">
-        <is>
-          <t>SWAMINATHAN</t>
-        </is>
-      </c>
+          <t>KIRUPANANDH</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr"/>
       <c r="E319" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -12890,12 +12612,12 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H319" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12627,17 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>CMS0348987</t>
+          <t>IPD0040766</t>
         </is>
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>KIRUPANANDH</t>
+          <t>MANIMEGALAI</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>SIVALINGAM</t>
+          <t>SWAMINATHAN</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -12925,15 +12647,15 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G320" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H320" s="3" t="inlineStr"/>
+          <t>15.</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr"/>
+      <c r="H320" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n">
@@ -13005,7 +12727,11 @@
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr"/>
-      <c r="H322" s="3" t="inlineStr"/>
+      <c r="H322" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n">
@@ -13036,11 +12762,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G323" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="G323" s="3" t="inlineStr"/>
       <c r="H323" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -13101,11 +12823,7 @@
           <t>YOGALAKSHMI</t>
         </is>
       </c>
-      <c r="D325" s="3" t="inlineStr">
-        <is>
-          <t>THIRUKODI</t>
-        </is>
-      </c>
+      <c r="D325" s="3" t="inlineStr"/>
       <c r="E325" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -13273,7 +12991,7 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -13281,7 +12999,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="H329" s="3" t="inlineStr"/>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n">
@@ -13432,11 +13154,7 @@
           <t>15B</t>
         </is>
       </c>
-      <c r="G333" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="G333" s="3" t="inlineStr"/>
       <c r="H333" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -13497,11 +13215,7 @@
           <t>GNANAPRAGASAM</t>
         </is>
       </c>
-      <c r="D335" s="3" t="inlineStr">
-        <is>
-          <t>SAVARIMUTHU</t>
-        </is>
-      </c>
+      <c r="D335" s="3" t="inlineStr"/>
       <c r="E335" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -13627,7 +13341,11 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F338" s="3" t="inlineStr"/>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
           <t>55</t>
@@ -13668,11 +13386,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="G339" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+      <c r="G339" s="3" t="inlineStr"/>
       <c r="H339" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -13688,16 +13402,8 @@
           <t>GKY0374876</t>
         </is>
       </c>
-      <c r="C340" s="3" t="inlineStr">
-        <is>
-          <t>GNANAPRAGASAM</t>
-        </is>
-      </c>
-      <c r="D340" s="3" t="inlineStr">
-        <is>
-          <t>GNANAPRAGASAM</t>
-        </is>
-      </c>
+      <c r="C340" s="3" t="inlineStr"/>
+      <c r="D340" s="3" t="inlineStr"/>
       <c r="E340" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -13868,7 +13574,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="G344" s="3" t="inlineStr"/>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="H344" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -13889,11 +13599,7 @@
           <t>SHAMIRA</t>
         </is>
       </c>
-      <c r="D345" s="3" t="inlineStr">
-        <is>
-          <t>ABDOUL HACKIM</t>
-        </is>
-      </c>
+      <c r="D345" s="3" t="inlineStr"/>
       <c r="E345" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -13921,12 +13627,12 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>IPO0069310</t>
+          <t>IIP0006931</t>
         </is>
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>MOHAMED SALMAN</t>
+          <t>ABDOUL HACKIM</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
@@ -13961,7 +13667,7 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>IPO0213231</t>
+          <t>IPD0213231</t>
         </is>
       </c>
       <c r="C347" s="3" t="inlineStr">
@@ -13981,7 +13687,7 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>16.</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -14041,37 +13747,37 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>IPD0005314</t>
+          <t>IPD0188219</t>
         </is>
       </c>
       <c r="C349" s="3" t="inlineStr">
         <is>
-          <t>Noorjahan</t>
+          <t>KHALID MOHAMMED</t>
         </is>
       </c>
       <c r="D349" s="3" t="inlineStr">
         <is>
-          <t>Abdul Kadar</t>
+          <t>KAMALUDIN</t>
         </is>
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>16D</t>
+          <t>164</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H349" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -14081,37 +13787,37 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>IPD0188219</t>
+          <t>IPD0005314</t>
         </is>
       </c>
       <c r="C350" s="3" t="inlineStr">
         <is>
-          <t>KHALID MOHAMMED</t>
+          <t>Noorjahan</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>KAMALUDIN</t>
+          <t>Abdul Kadar</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>16D</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H350" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -14184,11 +13890,7 @@
           <t>16D</t>
         </is>
       </c>
-      <c r="G352" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="G352" s="3" t="inlineStr"/>
       <c r="H352" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -14224,11 +13926,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G353" s="3" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+      <c r="G353" s="3" t="inlineStr"/>
       <c r="H353" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -14306,7 +14004,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H355" s="3" t="inlineStr">
@@ -14464,12 +14162,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G359" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="H359" s="3" t="inlineStr"/>
+      <c r="G359" s="3" t="inlineStr"/>
+      <c r="H359" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n">
@@ -14562,7 +14260,7 @@
       </c>
       <c r="C362" s="3" t="inlineStr">
         <is>
-          <t>TARIQ</t>
+          <t>ABDOUL RACHID</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
@@ -14642,7 +14340,7 @@
       </c>
       <c r="C364" s="3" t="inlineStr">
         <is>
-          <t>SELVAM</t>
+          <t>GEETHA</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
@@ -14722,7 +14420,7 @@
       </c>
       <c r="C366" s="3" t="inlineStr">
         <is>
-          <t>KASIRAJA</t>
+          <t>SOLAIAPPAN</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
@@ -14802,7 +14500,7 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>SANTHOSHKUMAR</t>
+          <t>SELVAM</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
@@ -14815,8 +14513,16 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F368" s="3" t="inlineStr"/>
-      <c r="G368" s="3" t="inlineStr"/>
+      <c r="F368" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G368" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -14869,7 +14575,7 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>IPO0021088</t>
+          <t>IPO0210880</t>
         </is>
       </c>
       <c r="C370" s="3" t="inlineStr">
@@ -14909,7 +14615,7 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>IPO0103473</t>
+          <t>IPD0103473</t>
         </is>
       </c>
       <c r="C371" s="3" t="inlineStr">
@@ -15047,16 +14753,8 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F374" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G374" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="F374" s="3" t="inlineStr"/>
+      <c r="G374" s="3" t="inlineStr"/>
       <c r="H374" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -15074,7 +14772,7 @@
       </c>
       <c r="C375" s="3" t="inlineStr">
         <is>
-          <t>INCIA</t>
+          <t>LINCIA</t>
         </is>
       </c>
       <c r="D375" s="3" t="inlineStr">
@@ -15114,7 +14812,7 @@
       </c>
       <c r="C376" s="3" t="inlineStr">
         <is>
-          <t>PUSHPA</t>
+          <t>SARAVANAN</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
@@ -15149,7 +14847,7 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>IPD0197426</t>
+          <t>IPO0197426</t>
         </is>
       </c>
       <c r="C377" s="3" t="inlineStr">
@@ -15167,11 +14865,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F377" s="3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+      <c r="F377" s="3" t="inlineStr"/>
       <c r="G377" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -15217,11 +14911,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H378" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H378" s="3" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="n">
@@ -15229,22 +14919,22 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>IPD0026625</t>
+          <t>IPD0103499</t>
         </is>
       </c>
       <c r="C379" s="3" t="inlineStr">
         <is>
-          <t>VIOLER SELVAKUMARI</t>
+          <t>JOHN VINCENT</t>
         </is>
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>JOHN VINCENT</t>
+          <t>JAYASEELAN</t>
         </is>
       </c>
       <c r="E379" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F379" s="3" t="inlineStr">
@@ -15254,12 +14944,12 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H379" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -15269,22 +14959,22 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>IPD0103499</t>
+          <t>IPD0026625</t>
         </is>
       </c>
       <c r="C380" s="3" t="inlineStr">
         <is>
+          <t>VIOLER SELVAKUMARI</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
           <t>JOHN VINCENT</t>
         </is>
       </c>
-      <c r="D380" s="3" t="inlineStr">
-        <is>
-          <t>JAYASEELAN</t>
-        </is>
-      </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr">
@@ -15292,14 +14982,10 @@
           <t>20</t>
         </is>
       </c>
-      <c r="G380" s="3" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+      <c r="G380" s="3" t="inlineStr"/>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -15357,11 +15043,7 @@
           <t>JOSHUA JABASTIN</t>
         </is>
       </c>
-      <c r="D382" s="3" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
+      <c r="D382" s="3" t="inlineStr"/>
       <c r="E382" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -15408,11 +15090,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="G383" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="G383" s="3" t="inlineStr"/>
       <c r="H383" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -15525,7 +15203,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>20B</t>
+          <t>20B.</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr"/>
@@ -15586,7 +15264,7 @@
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>MARIYA JOSEPH</t>
+          <t>REETHA</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
@@ -15689,11 +15367,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H390" s="3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+      <c r="H390" s="3" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="n">
@@ -15721,7 +15395,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -15759,11 +15433,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F392" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="F392" s="3" t="inlineStr"/>
       <c r="G392" s="3" t="inlineStr">
         <is>
           <t>44</t>
@@ -15799,11 +15469,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F393" s="3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="F393" s="3" t="inlineStr"/>
       <c r="G393" s="3" t="inlineStr">
         <is>
           <t>35</t>
@@ -15826,7 +15492,7 @@
       </c>
       <c r="C394" s="3" t="inlineStr">
         <is>
-          <t>KADIRAVAN</t>
+          <t>K DEVISRI</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
@@ -15879,11 +15545,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F395" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="F395" s="3" t="inlineStr"/>
       <c r="G395" s="3" t="inlineStr">
         <is>
           <t>58</t>
@@ -15959,7 +15621,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F397" s="3" t="inlineStr"/>
+      <c r="F397" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -15995,7 +15661,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F398" s="3" t="inlineStr"/>
+      <c r="F398" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -16031,7 +15701,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F399" s="3" t="inlineStr"/>
+      <c r="F399" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -16049,12 +15723,12 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>IPD0014456</t>
+          <t>IPO0014456</t>
         </is>
       </c>
       <c r="C400" s="3" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI</t>
+          <t>SIVAKUMAR</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
@@ -16089,7 +15763,7 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>IPO0005967</t>
+          <t>IPD0005967</t>
         </is>
       </c>
       <c r="C401" s="3" t="inlineStr">
@@ -16107,7 +15781,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F401" s="3" t="inlineStr"/>
+      <c r="F401" s="3" t="inlineStr">
+        <is>
+          <t>22-B</t>
+        </is>
+      </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
           <t>57</t>
@@ -16145,7 +15823,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>22-8</t>
+          <t>22-B</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -16170,7 +15848,7 @@
       </c>
       <c r="C403" s="3" t="inlineStr">
         <is>
-          <t>ELIZABETH</t>
+          <t>PAZHANISAMY</t>
         </is>
       </c>
       <c r="D403" s="3" t="inlineStr">
@@ -16210,7 +15888,7 @@
       </c>
       <c r="C404" s="3" t="inlineStr">
         <is>
-          <t>Kunaaran</t>
+          <t>Mayilvaran</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
@@ -16223,11 +15901,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F404" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="F404" s="3" t="inlineStr"/>
       <c r="G404" s="3" t="inlineStr">
         <is>
           <t>68</t>
@@ -16250,7 +15924,7 @@
       </c>
       <c r="C405" s="3" t="inlineStr">
         <is>
-          <t>Manonmani</t>
+          <t>Kunaaran</t>
         </is>
       </c>
       <c r="D405" s="3" t="inlineStr">
@@ -16263,11 +15937,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F405" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+      <c r="F405" s="3" t="inlineStr"/>
       <c r="G405" s="3" t="inlineStr">
         <is>
           <t>61</t>
@@ -16290,7 +15960,7 @@
       </c>
       <c r="C406" s="3" t="inlineStr">
         <is>
-          <t>KUSELAR</t>
+          <t>CHINNAMUTHU</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
@@ -16388,11 +16058,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="G408" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+      <c r="G408" s="3" t="inlineStr"/>
       <c r="H408" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -16405,17 +16071,17 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>GKY0412098</t>
+          <t>GKY0681817</t>
         </is>
       </c>
       <c r="C409" s="3" t="inlineStr">
         <is>
-          <t>Saravanan</t>
+          <t>VIJAYARANI</t>
         </is>
       </c>
       <c r="D409" s="3" t="inlineStr">
         <is>
-          <t>Karupaiya</t>
+          <t>PAHANISAMY</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr">
@@ -16430,12 +16096,12 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H409" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -16445,17 +16111,17 @@
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>GKY0681817</t>
+          <t>GKY0412098</t>
         </is>
       </c>
       <c r="C410" s="3" t="inlineStr">
         <is>
-          <t>VIJAYARANI</t>
+          <t>Saravanan</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>PAHANISAMY</t>
+          <t>Karupaiya</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
@@ -16470,12 +16136,12 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H410" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -16553,11 +16219,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="H412" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H412" s="3" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="n">
@@ -16628,7 +16290,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="G414" s="3" t="inlineStr"/>
+      <c r="G414" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H414" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -16700,11 +16366,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="G416" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="G416" s="3" t="inlineStr"/>
       <c r="H416" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -16737,7 +16399,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>23A</t>
+          <t>234,</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -16777,7 +16439,7 @@
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>23B</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
@@ -16917,7 +16579,7 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>JTP0449912</t>
+          <t>JTP0449512</t>
         </is>
       </c>
       <c r="C422" s="3" t="inlineStr">
@@ -16936,11 +16598,7 @@
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
-      <c r="G422" s="3" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
+      <c r="G422" s="3" t="inlineStr"/>
       <c r="H422" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -16976,7 +16634,11 @@
           <t>25</t>
         </is>
       </c>
-      <c r="G423" s="3" t="inlineStr"/>
+      <c r="G423" s="3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="H423" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -16994,7 +16656,7 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>Chitra</t>
+          <t>Sankar</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
@@ -17034,7 +16696,7 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>KAVITHA</t>
+          <t>SUBRAMANI</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
@@ -17154,25 +16816,25 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
+          <t>PUVIARASI</t>
+        </is>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
           <t>RAJAPANDIAN</t>
         </is>
       </c>
-      <c r="D428" s="3" t="inlineStr">
-        <is>
-          <t>RAJAPANDIAN</t>
-        </is>
-      </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
         </is>
       </c>
-      <c r="F428" s="3" t="inlineStr"/>
-      <c r="G428" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="F428" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G428" s="3" t="inlineStr"/>
       <c r="H428" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17228,16 +16890,8 @@
           <t>ZHN0067983</t>
         </is>
       </c>
-      <c r="C430" s="3" t="inlineStr">
-        <is>
-          <t>PONNUSAMY</t>
-        </is>
-      </c>
-      <c r="D430" s="3" t="inlineStr">
-        <is>
-          <t>PONNUSAMY</t>
-        </is>
-      </c>
+      <c r="C430" s="3" t="inlineStr"/>
+      <c r="D430" s="3" t="inlineStr"/>
       <c r="E430" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -17285,14 +16939,10 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G431" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+          <t>25,</t>
+        </is>
+      </c>
+      <c r="G431" s="3" t="inlineStr"/>
       <c r="H431" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17385,7 +17035,7 @@
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>IPD0128611</t>
+          <t>IPO0128611</t>
         </is>
       </c>
       <c r="C434" s="3" t="inlineStr">
@@ -17468,11 +17118,7 @@
           <t>ULJ0018853</t>
         </is>
       </c>
-      <c r="C436" s="3" t="inlineStr">
-        <is>
-          <t>MUTHU</t>
-        </is>
-      </c>
+      <c r="C436" s="3" t="inlineStr"/>
       <c r="D436" s="3" t="inlineStr">
         <is>
           <t>SUBANISVARI</t>
@@ -17505,7 +17151,7 @@
       </c>
       <c r="B437" s="3" t="inlineStr">
         <is>
-          <t>IPO0092163</t>
+          <t>IPD0092163</t>
         </is>
       </c>
       <c r="C437" s="3" t="inlineStr">
@@ -17523,11 +17169,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F437" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="F437" s="3" t="inlineStr"/>
       <c r="G437" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -17553,11 +17195,7 @@
           <t>manoen mani</t>
         </is>
       </c>
-      <c r="D438" s="3" t="inlineStr">
-        <is>
-          <t>rajamani</t>
-        </is>
-      </c>
+      <c r="D438" s="3" t="inlineStr"/>
       <c r="E438" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -17573,11 +17211,7 @@
           <t>74</t>
         </is>
       </c>
-      <c r="H438" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H438" s="3" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="n">
@@ -17585,17 +17219,17 @@
       </c>
       <c r="B439" s="3" t="inlineStr">
         <is>
-          <t>GKY0409219</t>
+          <t>IPD0011726</t>
         </is>
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>MANIMEGALAI</t>
+          <t>GILDA MARY</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
         <is>
-          <t>GOPAL</t>
+          <t>ANTHONISAMY</t>
         </is>
       </c>
       <c r="E439" s="3" t="inlineStr">
@@ -17608,11 +17242,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="G439" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+      <c r="G439" s="3" t="inlineStr"/>
       <c r="H439" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17625,17 +17255,17 @@
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>IPD0011726</t>
+          <t>GKY0409219</t>
         </is>
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>GILDA MARY</t>
+          <t>MANIMEGALAI</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>ANTHONISAMY</t>
+          <t>GOPAL</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
@@ -17648,11 +17278,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="G440" s="3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="G440" s="3" t="inlineStr"/>
       <c r="H440" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17673,7 +17299,11 @@
           <t>HARIHARAN</t>
         </is>
       </c>
-      <c r="D441" s="3" t="inlineStr"/>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>MANIMEGALAI</t>
+        </is>
+      </c>
       <c r="E441" s="3" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -17747,7 +17377,7 @@
       </c>
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>Anthony sary</t>
+          <t>Anthony samy</t>
         </is>
       </c>
       <c r="E443" s="3" t="inlineStr">
@@ -17761,7 +17391,11 @@
         </is>
       </c>
       <c r="G443" s="3" t="inlineStr"/>
-      <c r="H443" s="3" t="inlineStr"/>
+      <c r="H443" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="3" t="n">
@@ -17849,7 +17483,7 @@
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>BQG0196976</t>
+          <t>BQG0196576</t>
         </is>
       </c>
       <c r="C446" s="3" t="inlineStr">
@@ -17934,7 +17568,7 @@
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>KANNAN</t>
+          <t>SUSILA</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
@@ -18054,7 +17688,7 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>BASKARAN</t>
+          <t>SELVI</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
@@ -18125,7 +17759,7 @@
       </c>
       <c r="B453" s="3" t="inlineStr">
         <is>
-          <t>DGL0025840</t>
+          <t>DGL0258400</t>
         </is>
       </c>
       <c r="C453" s="3" t="inlineStr">
@@ -18170,7 +17804,7 @@
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>RADHAKRISHNAN</t>
+          <t>SASIKALA</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
@@ -18210,7 +17844,7 @@
       </c>
       <c r="C455" s="3" t="inlineStr">
         <is>
-          <t>BASKARAN</t>
+          <t>RAMYA</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
@@ -18340,11 +17974,7 @@
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr"/>
-      <c r="G458" s="3" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+      <c r="G458" s="3" t="inlineStr"/>
       <c r="H458" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -18377,7 +18007,7 @@
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
-          <t>29-4</t>
+          <t>29-A</t>
         </is>
       </c>
       <c r="G459" s="3" t="inlineStr">
@@ -18497,7 +18127,7 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>29/A</t>
+          <t>29/4</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
@@ -18580,11 +18210,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="G464" s="3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="G464" s="3" t="inlineStr"/>
       <c r="H464" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -18640,16 +18266,8 @@
           <t>KVY0691642</t>
         </is>
       </c>
-      <c r="C466" s="3" t="inlineStr">
-        <is>
-          <t>BALASUBRAMANIAN</t>
-        </is>
-      </c>
-      <c r="D466" s="3" t="inlineStr">
-        <is>
-          <t>BALASUBRAMANIAN</t>
-        </is>
-      </c>
+      <c r="C466" s="3" t="inlineStr"/>
+      <c r="D466" s="3" t="inlineStr"/>
       <c r="E466" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -18700,11 +18318,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="G467" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="G467" s="3" t="inlineStr"/>
       <c r="H467" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -18737,14 +18351,10 @@
       </c>
       <c r="F468" s="3" t="inlineStr">
         <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="G468" s="3" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G468" s="3" t="inlineStr"/>
       <c r="H468" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -18757,22 +18367,22 @@
       </c>
       <c r="B469" s="3" t="inlineStr">
         <is>
-          <t>GKY0580506</t>
+          <t>GKY0373894</t>
         </is>
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>MALAIKANI</t>
+          <t>Dhanam</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
         <is>
-          <t>RAMAR</t>
+          <t>Balasubramaniyan</t>
         </is>
       </c>
       <c r="E469" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F469" s="3" t="inlineStr">
@@ -18782,12 +18392,12 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H469" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -18797,22 +18407,22 @@
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>GKY0373894</t>
+          <t>GKY0580506</t>
         </is>
       </c>
       <c r="C470" s="3" t="inlineStr">
         <is>
-          <t>Dhanam</t>
+          <t>MALAIKANI</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>Balasubramaniyan</t>
+          <t>RAMAR</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr">
@@ -18822,12 +18432,12 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H470" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -18900,12 +18510,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="G472" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H472" s="3" t="inlineStr"/>
+      <c r="G472" s="3" t="inlineStr"/>
+      <c r="H472" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="3" t="n">
@@ -18937,7 +18547,11 @@
         </is>
       </c>
       <c r="G473" s="3" t="inlineStr"/>
-      <c r="H473" s="3" t="inlineStr"/>
+      <c r="H473" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="3" t="n">
@@ -19070,7 +18684,7 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>Manimegalai</t>
+          <t>Manimegalal</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
@@ -19113,11 +18727,7 @@
           <t>KRISHNAVENI ALIAS GIRIJA</t>
         </is>
       </c>
-      <c r="D478" s="3" t="inlineStr">
-        <is>
-          <t>NAGARAJAN</t>
-        </is>
-      </c>
+      <c r="D478" s="3" t="inlineStr"/>
       <c r="E478" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -19128,7 +18738,11 @@
           <t>32</t>
         </is>
       </c>
-      <c r="G478" s="3" t="inlineStr"/>
+      <c r="G478" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="H478" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -19161,7 +18775,11 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H479" s="3" t="inlineStr"/>
+      <c r="H479" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="3" t="n">
@@ -19227,7 +18845,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F481" s="3" t="inlineStr"/>
+      <c r="F481" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -19304,11 +18926,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="G483" s="3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="G483" s="3" t="inlineStr"/>
       <c r="H483" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -19326,7 +18944,7 @@
       </c>
       <c r="C484" s="3" t="inlineStr">
         <is>
-          <t>VAITHIYANATHAN</t>
+          <t>JAGADHA</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
@@ -19500,11 +19118,7 @@
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr"/>
-      <c r="G488" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="G488" s="3" t="inlineStr"/>
       <c r="H488" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -19615,11 +19229,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F491" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="F491" s="3" t="inlineStr"/>
       <c r="G491" s="3" t="inlineStr">
         <is>
           <t>70</t>
@@ -19735,11 +19345,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F494" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="F494" s="3" t="inlineStr"/>
       <c r="G494" s="3" t="inlineStr"/>
       <c r="H494" s="3" t="inlineStr">
         <is>
@@ -19753,7 +19359,7 @@
       </c>
       <c r="B495" s="3" t="inlineStr">
         <is>
-          <t>ABO0044850</t>
+          <t>ABQ0448506</t>
         </is>
       </c>
       <c r="C495" s="3" t="inlineStr">
@@ -19763,7 +19369,7 @@
       </c>
       <c r="D495" s="3" t="inlineStr">
         <is>
-          <t>Chellian</t>
+          <t>Chelliah</t>
         </is>
       </c>
       <c r="E495" s="3" t="inlineStr">
@@ -19798,7 +19404,7 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>MURUGESAN</t>
+          <t>SHANMUGAM</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
@@ -19913,22 +19519,22 @@
       </c>
       <c r="B499" s="3" t="inlineStr">
         <is>
-          <t>ULJ0002915</t>
+          <t>GKY0665364</t>
         </is>
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>VEERAMUTHU</t>
+          <t>EDWARD</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>VEERAMUTHU</t>
+          <t>JOHNPETER</t>
         </is>
       </c>
       <c r="E499" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F499" s="3" t="inlineStr">
@@ -19936,10 +19542,14 @@
           <t>34</t>
         </is>
       </c>
-      <c r="G499" s="3" t="inlineStr"/>
+      <c r="G499" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="H499" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -19949,22 +19559,22 @@
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>GKY0665364</t>
+          <t>ULJ0002915</t>
         </is>
       </c>
       <c r="C500" s="3" t="inlineStr">
         <is>
-          <t>EDWARD</t>
+          <t>UMA</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>JOHNPETER</t>
+          <t>VEERAMUTHU</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F500" s="3" t="inlineStr">
@@ -19972,14 +19582,10 @@
           <t>34</t>
         </is>
       </c>
-      <c r="G500" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="G500" s="3" t="inlineStr"/>
       <c r="H500" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -20109,11 +19715,7 @@
           <t>SIVAPRIYA SIVAPRIYA</t>
         </is>
       </c>
-      <c r="D504" s="3" t="inlineStr">
-        <is>
-          <t>UMA VEERAMUTHU</t>
-        </is>
-      </c>
+      <c r="D504" s="3" t="inlineStr"/>
       <c r="E504" s="3" t="inlineStr">
         <is>
           <t>Mother</t>
@@ -20129,7 +19731,11 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H504" s="3" t="inlineStr"/>
+      <c r="H504" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="3" t="n">
@@ -20153,7 +19759,7 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>344A,</t>
+          <t>344,</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
@@ -20193,7 +19799,7 @@
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>344,</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
@@ -20353,7 +19959,7 @@
       </c>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>34B</t>
+          <t>348</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr">
@@ -20414,7 +20020,7 @@
       </c>
       <c r="B512" s="3" t="inlineStr">
         <is>
-          <t>JTP0527556</t>
+          <t>JTP0052755</t>
         </is>
       </c>
       <c r="C512" s="3" t="inlineStr">
@@ -20539,21 +20145,13 @@
           <t>ASHOKKUMAR</t>
         </is>
       </c>
-      <c r="D515" s="3" t="inlineStr">
-        <is>
-          <t>THONTHIAPPAN</t>
-        </is>
-      </c>
+      <c r="D515" s="3" t="inlineStr"/>
       <c r="E515" s="3" t="inlineStr">
         <is>
           <t>Father</t>
         </is>
       </c>
-      <c r="F515" s="3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="F515" s="3" t="inlineStr"/>
       <c r="G515" s="3" t="inlineStr">
         <is>
           <t>46</t>
@@ -20659,17 +20257,17 @@
           <t>NATHIYA MARY</t>
         </is>
       </c>
-      <c r="D518" s="3" t="inlineStr">
-        <is>
-          <t>ASHOK KUMAR</t>
-        </is>
-      </c>
+      <c r="D518" s="3" t="inlineStr"/>
       <c r="E518" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
         </is>
       </c>
-      <c r="F518" s="3" t="inlineStr"/>
+      <c r="F518" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
           <t>39</t>
@@ -20732,7 +20330,7 @@
       </c>
       <c r="C520" s="3" t="inlineStr">
         <is>
-          <t>Ramasamy</t>
+          <t>Durairaj</t>
         </is>
       </c>
       <c r="D520" s="3" t="inlineStr">
@@ -20787,7 +20385,7 @@
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>36.</t>
         </is>
       </c>
       <c r="G521" s="3" t="inlineStr">
@@ -20910,7 +20508,11 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G524" s="3" t="inlineStr"/>
+      <c r="G524" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="H524" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -20968,7 +20570,7 @@
       </c>
       <c r="C526" s="3" t="inlineStr">
         <is>
-          <t>VIGNESH</t>
+          <t>MARIAPPAN</t>
         </is>
       </c>
       <c r="D526" s="3" t="inlineStr">
@@ -21003,7 +20605,7 @@
       </c>
       <c r="B527" s="3" t="inlineStr">
         <is>
-          <t>IPO0008739</t>
+          <t>IPO0087395</t>
         </is>
       </c>
       <c r="C527" s="3" t="inlineStr">
@@ -21026,11 +20628,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G527" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
+      <c r="G527" s="3" t="inlineStr"/>
       <c r="H527" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -21083,17 +20681,17 @@
       </c>
       <c r="B529" s="3" t="inlineStr">
         <is>
-          <t>AJJ0048033</t>
+          <t>IPD0202440</t>
         </is>
       </c>
       <c r="C529" s="3" t="inlineStr">
         <is>
-          <t>ANANDHI</t>
+          <t>KIRUTHIGA</t>
         </is>
       </c>
       <c r="D529" s="3" t="inlineStr">
         <is>
-          <t>KANNAN</t>
+          <t>GANESAN</t>
         </is>
       </c>
       <c r="E529" s="3" t="inlineStr">
@@ -21103,14 +20701,10 @@
       </c>
       <c r="F529" s="3" t="inlineStr">
         <is>
-          <t>36/52</t>
-        </is>
-      </c>
-      <c r="G529" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G529" s="3" t="inlineStr"/>
       <c r="H529" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21123,17 +20717,17 @@
       </c>
       <c r="B530" s="3" t="inlineStr">
         <is>
-          <t>IPD0202440</t>
+          <t>AJJ0048033</t>
         </is>
       </c>
       <c r="C530" s="3" t="inlineStr">
         <is>
-          <t>KIRUTHIGA</t>
+          <t>ANANDHI</t>
         </is>
       </c>
       <c r="D530" s="3" t="inlineStr">
         <is>
-          <t>GANESAN</t>
+          <t>KANNAN</t>
         </is>
       </c>
       <c r="E530" s="3" t="inlineStr">
@@ -21143,14 +20737,10 @@
       </c>
       <c r="F530" s="3" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G530" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>36/52</t>
+        </is>
+      </c>
+      <c r="G530" s="3" t="inlineStr"/>
       <c r="H530" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21251,11 +20841,7 @@
           <t>GAYATHRI</t>
         </is>
       </c>
-      <c r="D533" s="3" t="inlineStr">
-        <is>
-          <t>DINESHKUMAR</t>
-        </is>
-      </c>
+      <c r="D533" s="3" t="inlineStr"/>
       <c r="E533" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -21266,11 +20852,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="G533" s="3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="G533" s="3" t="inlineStr"/>
       <c r="H533" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21323,7 +20905,7 @@
       </c>
       <c r="B535" s="3" t="inlineStr">
         <is>
-          <t>IPO0105379</t>
+          <t>IPD0105379</t>
         </is>
       </c>
       <c r="C535" s="3" t="inlineStr">
@@ -21431,7 +21013,11 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H537" s="3" t="inlineStr"/>
+      <c r="H537" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="3" t="n">
@@ -21591,19 +21177,19 @@
       </c>
       <c r="B542" s="3" t="inlineStr">
         <is>
-          <t>IPO0014464</t>
+          <t>IPD0014464</t>
         </is>
       </c>
       <c r="C542" s="3" t="inlineStr">
         <is>
+          <t>THIRUKODI</t>
+        </is>
+      </c>
+      <c r="D542" s="3" t="inlineStr">
+        <is>
           <t>NAMBIRAJAN</t>
         </is>
       </c>
-      <c r="D542" s="3" t="inlineStr">
-        <is>
-          <t>NAMBIRAJAN</t>
-        </is>
-      </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -21614,11 +21200,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="G542" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="G542" s="3" t="inlineStr"/>
       <c r="H542" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -21631,7 +21213,7 @@
       </c>
       <c r="B543" s="3" t="inlineStr">
         <is>
-          <t>IPD0004050</t>
+          <t>IPO0040501</t>
         </is>
       </c>
       <c r="C543" s="3" t="inlineStr">
@@ -21651,7 +21233,7 @@
       </c>
       <c r="F543" s="3" t="inlineStr">
         <is>
-          <t>: 38</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G543" s="3" t="inlineStr">
@@ -21676,7 +21258,7 @@
       </c>
       <c r="C544" s="3" t="inlineStr">
         <is>
-          <t>ARIKRISHNAN</t>
+          <t>RAVISANKAR</t>
         </is>
       </c>
       <c r="D544" s="3" t="inlineStr">
@@ -21731,7 +21313,7 @@
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>384.</t>
         </is>
       </c>
       <c r="G545" s="3" t="inlineStr">
@@ -21771,7 +21353,7 @@
       </c>
       <c r="F546" s="3" t="inlineStr">
         <is>
-          <t>38-4</t>
+          <t>38-A</t>
         </is>
       </c>
       <c r="G546" s="3" t="inlineStr">
@@ -21855,11 +21437,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="H548" s="3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+      <c r="H548" s="3" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="3" t="n">
@@ -21910,16 +21488,8 @@
           <t>IPO0028175</t>
         </is>
       </c>
-      <c r="C550" s="3" t="inlineStr">
-        <is>
-          <t>KRISHNAN</t>
-        </is>
-      </c>
-      <c r="D550" s="3" t="inlineStr">
-        <is>
-          <t>KRISHNAN</t>
-        </is>
-      </c>
+      <c r="C550" s="3" t="inlineStr"/>
+      <c r="D550" s="3" t="inlineStr"/>
       <c r="E550" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -21947,7 +21517,7 @@
       </c>
       <c r="B551" s="3" t="inlineStr">
         <is>
-          <t>IPO0086751</t>
+          <t>IPD0086751</t>
         </is>
       </c>
       <c r="C551" s="3" t="inlineStr">
@@ -21992,7 +21562,7 @@
       </c>
       <c r="C552" s="3" t="inlineStr">
         <is>
-          <t>Thaiyanayagi</t>
+          <t>Thalyanayagi</t>
         </is>
       </c>
       <c r="D552" s="3" t="inlineStr">
@@ -22032,7 +21602,7 @@
       </c>
       <c r="C553" s="3" t="inlineStr">
         <is>
-          <t>PACHAIPPAN</t>
+          <t>ANJALAI</t>
         </is>
       </c>
       <c r="D553" s="3" t="inlineStr">
@@ -22072,14 +21642,14 @@
       </c>
       <c r="C554" s="3" t="inlineStr">
         <is>
+          <t>Tamilarasi</t>
+        </is>
+      </c>
+      <c r="D554" s="3" t="inlineStr">
+        <is>
           <t>Gopalakrishnan</t>
         </is>
       </c>
-      <c r="D554" s="3" t="inlineStr">
-        <is>
-          <t>Gopalakrishnan</t>
-        </is>
-      </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -22087,7 +21657,7 @@
       </c>
       <c r="F554" s="3" t="inlineStr">
         <is>
-          <t>39B</t>
+          <t>39B.</t>
         </is>
       </c>
       <c r="G554" s="3" t="inlineStr"/>
@@ -22111,7 +21681,11 @@
           <t>PERUMAL</t>
         </is>
       </c>
-      <c r="D555" s="3" t="inlineStr"/>
+      <c r="D555" s="3" t="inlineStr">
+        <is>
+          <t>ELUMALAI</t>
+        </is>
+      </c>
       <c r="E555" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -22139,12 +21713,12 @@
       </c>
       <c r="B556" s="3" t="inlineStr">
         <is>
-          <t>GKY0669406</t>
+          <t>GKY0665406</t>
         </is>
       </c>
       <c r="C556" s="3" t="inlineStr">
         <is>
-          <t>SARQJA</t>
+          <t>PERUMAL</t>
         </is>
       </c>
       <c r="D556" s="3" t="inlineStr">
@@ -22242,11 +21816,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="G558" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="G558" s="3" t="inlineStr"/>
       <c r="H558" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22259,17 +21829,17 @@
       </c>
       <c r="B559" s="3" t="inlineStr">
         <is>
-          <t>GKY0360404</t>
+          <t>IPD0076034</t>
         </is>
       </c>
       <c r="C559" s="3" t="inlineStr">
         <is>
-          <t>Goudhaman ALIAS Selvaraj</t>
+          <t>MANIKKAM</t>
         </is>
       </c>
       <c r="D559" s="3" t="inlineStr">
         <is>
-          <t>Shanmugam</t>
+          <t>MANIKKAM</t>
         </is>
       </c>
       <c r="E559" s="3" t="inlineStr">
@@ -22282,7 +21852,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="G559" s="3" t="inlineStr"/>
+      <c r="G559" s="3" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="H559" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -22295,17 +21869,17 @@
       </c>
       <c r="B560" s="3" t="inlineStr">
         <is>
-          <t>IPD0076034</t>
+          <t>GKY0360404</t>
         </is>
       </c>
       <c r="C560" s="3" t="inlineStr">
         <is>
-          <t>ELUMALAI</t>
+          <t>Goudhaman ALIAS Selvaraj</t>
         </is>
       </c>
       <c r="D560" s="3" t="inlineStr">
         <is>
-          <t>MANIKKAM</t>
+          <t>Shanmugam</t>
         </is>
       </c>
       <c r="E560" s="3" t="inlineStr">
@@ -22318,11 +21892,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="G560" s="3" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="G560" s="3" t="inlineStr"/>
       <c r="H560" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -22343,12 +21913,7 @@
           <t>M</t>
         </is>
       </c>
-      <c r="D561" s="3" t="inlineStr">
-        <is>
-          <t>Goudhaman ALIAS
-Selvaraj Photo</t>
-        </is>
-      </c>
+      <c r="D561" s="3" t="inlineStr"/>
       <c r="E561" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -22439,11 +22004,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="G563" s="3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+      <c r="G563" s="3" t="inlineStr"/>
       <c r="H563" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22504,7 +22065,11 @@
           <t>RAJAKUMARI</t>
         </is>
       </c>
-      <c r="D565" s="3" t="inlineStr"/>
+      <c r="D565" s="3" t="inlineStr">
+        <is>
+          <t>KRISHNAMOORTHY</t>
+        </is>
+      </c>
       <c r="E565" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -22680,7 +22245,11 @@
           <t>25</t>
         </is>
       </c>
-      <c r="H569" s="3" t="inlineStr"/>
+      <c r="H569" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="3" t="n">
@@ -22696,12 +22265,7 @@
           <t>KRISHNAKUMAR</t>
         </is>
       </c>
-      <c r="D570" s="3" t="inlineStr">
-        <is>
-          <t>GOWTHAMON ALIAS
-SELVARAJ Photo</t>
-        </is>
-      </c>
+      <c r="D570" s="3" t="inlineStr"/>
       <c r="E570" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -22709,7 +22273,7 @@
       </c>
       <c r="F570" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>47</t>
         </is>
       </c>
       <c r="G570" s="3" t="inlineStr">
@@ -22770,7 +22334,7 @@
       </c>
       <c r="B572" s="3" t="inlineStr">
         <is>
-          <t>IPD0196434</t>
+          <t>IPD0196436</t>
         </is>
       </c>
       <c r="C572" s="3" t="inlineStr">
@@ -22778,11 +22342,7 @@
           <t>KARTHIK</t>
         </is>
       </c>
-      <c r="D572" s="3" t="inlineStr">
-        <is>
-          <t>EZHUMLAI</t>
-        </is>
-      </c>
+      <c r="D572" s="3" t="inlineStr"/>
       <c r="E572" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -22821,11 +22381,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="G573" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="G573" s="3" t="inlineStr"/>
       <c r="H573" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -23016,7 +22572,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F578" s="3" t="inlineStr"/>
+      <c r="F578" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="G578" s="3" t="inlineStr">
         <is>
           <t>47</t>
@@ -23074,19 +22634,11 @@
       </c>
       <c r="B580" s="3" t="inlineStr">
         <is>
-          <t>JTP0534433</t>
-        </is>
-      </c>
-      <c r="C580" s="3" t="inlineStr">
-        <is>
-          <t>SELVI</t>
-        </is>
-      </c>
-      <c r="D580" s="3" t="inlineStr">
-        <is>
-          <t>MURUKASAN</t>
-        </is>
-      </c>
+          <t>JTP0534453</t>
+        </is>
+      </c>
+      <c r="C580" s="3" t="inlineStr"/>
+      <c r="D580" s="3" t="inlineStr"/>
       <c r="E580" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -23094,7 +22646,7 @@
       </c>
       <c r="F580" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>43.</t>
         </is>
       </c>
       <c r="G580" s="3" t="inlineStr">
@@ -23134,7 +22686,7 @@
       </c>
       <c r="F581" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>43.</t>
         </is>
       </c>
       <c r="G581" s="3" t="inlineStr">
@@ -23142,11 +22694,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="H581" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H581" s="3" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="3" t="n">
@@ -23154,7 +22702,7 @@
       </c>
       <c r="B582" s="3" t="inlineStr">
         <is>
-          <t>IPO0208504</t>
+          <t>IPD0208504</t>
         </is>
       </c>
       <c r="C582" s="3" t="inlineStr">
@@ -23257,11 +22805,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="G584" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+      <c r="G584" s="3" t="inlineStr"/>
       <c r="H584" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -23314,7 +22858,7 @@
       </c>
       <c r="B586" s="3" t="inlineStr">
         <is>
-          <t>IPO0216267</t>
+          <t>IIP0002162</t>
         </is>
       </c>
       <c r="C586" s="3" t="inlineStr">
@@ -23434,37 +22978,33 @@
       </c>
       <c r="B589" s="3" t="inlineStr">
         <is>
-          <t>GKY0428433</t>
+          <t>IPD0075945</t>
         </is>
       </c>
       <c r="C589" s="3" t="inlineStr">
         <is>
-          <t>Ravichandran</t>
+          <t>JAYANTHI</t>
         </is>
       </c>
       <c r="D589" s="3" t="inlineStr">
         <is>
-          <t>Nadesan</t>
+          <t>MANIKANDAN</t>
         </is>
       </c>
       <c r="E589" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F589" s="3" t="inlineStr">
         <is>
-          <t>45-B</t>
-        </is>
-      </c>
-      <c r="G589" s="3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G589" s="3" t="inlineStr"/>
       <c r="H589" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -23474,37 +23014,37 @@
       </c>
       <c r="B590" s="3" t="inlineStr">
         <is>
-          <t>IPD0075945</t>
+          <t>GKY0428433</t>
         </is>
       </c>
       <c r="C590" s="3" t="inlineStr">
         <is>
-          <t>JAYANTHI</t>
+          <t>Ravichandran</t>
         </is>
       </c>
       <c r="D590" s="3" t="inlineStr">
         <is>
-          <t>MANIKANDAN</t>
+          <t>Nadesan</t>
         </is>
       </c>
       <c r="E590" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F590" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>45-B</t>
         </is>
       </c>
       <c r="G590" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H590" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -23670,7 +23210,7 @@
       </c>
       <c r="B595" s="3" t="inlineStr">
         <is>
-          <t>IPD0080833</t>
+          <t>IPD0080853</t>
         </is>
       </c>
       <c r="C595" s="3" t="inlineStr">
@@ -23710,17 +23250,17 @@
       </c>
       <c r="B596" s="3" t="inlineStr">
         <is>
-          <t>IPO0203760</t>
+          <t>IIP0020376</t>
         </is>
       </c>
       <c r="C596" s="3" t="inlineStr">
         <is>
-          <t>BALAKUMAR</t>
+          <t>Patchaipiltai</t>
         </is>
       </c>
       <c r="D596" s="3" t="inlineStr">
         <is>
-          <t>Patchaipillai</t>
+          <t>Patchaipiltai</t>
         </is>
       </c>
       <c r="E596" s="3" t="inlineStr">
@@ -23733,7 +23273,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="G596" s="3" t="inlineStr"/>
+      <c r="G596" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H596" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -23854,7 +23398,11 @@
           <t>37</t>
         </is>
       </c>
-      <c r="H599" s="3" t="inlineStr"/>
+      <c r="H599" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="3" t="n">
@@ -24027,7 +23575,7 @@
       </c>
       <c r="C604" s="3" t="inlineStr">
         <is>
-          <t>RAMESH</t>
+          <t>KAVITHA</t>
         </is>
       </c>
       <c r="D604" s="3" t="inlineStr">
@@ -24062,7 +23610,7 @@
       </c>
       <c r="B605" s="3" t="inlineStr">
         <is>
-          <t>IPD0222075</t>
+          <t>IPO0222075</t>
         </is>
       </c>
       <c r="C605" s="3" t="inlineStr">
@@ -24085,11 +23633,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="G605" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="G605" s="3" t="inlineStr"/>
       <c r="H605" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -24200,7 +23744,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F608" s="3" t="inlineStr"/>
+      <c r="F608" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="G608" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -24241,11 +23789,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="G609" s="3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="G609" s="3" t="inlineStr"/>
       <c r="H609" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -24261,16 +23805,8 @@
           <t>IPO0105817</t>
         </is>
       </c>
-      <c r="C610" s="3" t="inlineStr">
-        <is>
-          <t>Sabapathy</t>
-        </is>
-      </c>
-      <c r="D610" s="3" t="inlineStr">
-        <is>
-          <t>Sabapathy</t>
-        </is>
-      </c>
+      <c r="C610" s="3" t="inlineStr"/>
+      <c r="D610" s="3" t="inlineStr"/>
       <c r="E610" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -24298,7 +23834,7 @@
       </c>
       <c r="B611" s="3" t="inlineStr">
         <is>
-          <t>IPO0105908</t>
+          <t>IPD0105908</t>
         </is>
       </c>
       <c r="C611" s="3" t="inlineStr">
@@ -24338,7 +23874,7 @@
       </c>
       <c r="B612" s="3" t="inlineStr">
         <is>
-          <t>IPO0105916</t>
+          <t>IPD0105916</t>
         </is>
       </c>
       <c r="C612" s="3" t="inlineStr">
@@ -24361,11 +23897,7 @@
           <t>49</t>
         </is>
       </c>
-      <c r="G612" s="3" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+      <c r="G612" s="3" t="inlineStr"/>
       <c r="H612" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -24423,14 +23955,14 @@
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
+          <t>DEVI</t>
+        </is>
+      </c>
+      <c r="D614" s="3" t="inlineStr">
+        <is>
           <t>KATHIRVEL</t>
         </is>
       </c>
-      <c r="D614" s="3" t="inlineStr">
-        <is>
-          <t>KATHIRVEL</t>
-        </is>
-      </c>
       <c r="E614" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -24441,7 +23973,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="G614" s="3" t="inlineStr"/>
+      <c r="G614" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H614" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -24499,7 +24035,7 @@
       </c>
       <c r="C616" s="3" t="inlineStr">
         <is>
-          <t>JAYARAMAN</t>
+          <t>THANGAPPAN</t>
         </is>
       </c>
       <c r="D616" s="3" t="inlineStr">
@@ -24517,11 +24053,7 @@
           <t>49</t>
         </is>
       </c>
-      <c r="G616" s="3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="G616" s="3" t="inlineStr"/>
       <c r="H616" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -24574,7 +24106,7 @@
       </c>
       <c r="B618" s="3" t="inlineStr">
         <is>
-          <t>JTP0354530</t>
+          <t>JTP0035453</t>
         </is>
       </c>
       <c r="C618" s="3" t="inlineStr">
@@ -24597,11 +24129,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="G618" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
+      <c r="G618" s="3" t="inlineStr"/>
       <c r="H618" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -24614,17 +24142,17 @@
       </c>
       <c r="B619" s="3" t="inlineStr">
         <is>
-          <t>IPD0105932</t>
+          <t>IPD0199133</t>
         </is>
       </c>
       <c r="C619" s="3" t="inlineStr">
         <is>
-          <t>JOSHEPH ARULSAMY</t>
+          <t>saravanan</t>
         </is>
       </c>
       <c r="D619" s="3" t="inlineStr">
         <is>
-          <t>RAJAMANICKAM</t>
+          <t>MURUGANANDHAM</t>
         </is>
       </c>
       <c r="E619" s="3" t="inlineStr">
@@ -24634,12 +24162,12 @@
       </c>
       <c r="F619" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G619" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H619" s="3" t="inlineStr">
@@ -24654,17 +24182,17 @@
       </c>
       <c r="B620" s="3" t="inlineStr">
         <is>
-          <t>IPD0199133</t>
+          <t>IPD0105932</t>
         </is>
       </c>
       <c r="C620" s="3" t="inlineStr">
         <is>
-          <t>saravanan</t>
+          <t>JOSHEPH ARULSAMY</t>
         </is>
       </c>
       <c r="D620" s="3" t="inlineStr">
         <is>
-          <t>MURUGANANDHAM</t>
+          <t>RAJAMANICKAM</t>
         </is>
       </c>
       <c r="E620" s="3" t="inlineStr">
@@ -24674,14 +24202,10 @@
       </c>
       <c r="F620" s="3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="G620" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="G620" s="3" t="inlineStr"/>
       <c r="H620" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -24699,12 +24223,12 @@
       </c>
       <c r="C621" s="3" t="inlineStr">
         <is>
-          <t>Ganansoundari</t>
+          <t>Ganansoundar</t>
         </is>
       </c>
       <c r="D621" s="3" t="inlineStr">
         <is>
-          <t>Josheph Arulsamy</t>
+          <t>Josheph Arulsarny</t>
         </is>
       </c>
       <c r="E621" s="3" t="inlineStr">
@@ -24722,7 +24246,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="H621" s="3" t="inlineStr"/>
+      <c r="H621" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="3" t="n">
@@ -24793,11 +24321,7 @@
           <t>51</t>
         </is>
       </c>
-      <c r="G623" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="G623" s="3" t="inlineStr"/>
       <c r="H623" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -24930,7 +24454,7 @@
       </c>
       <c r="B627" s="3" t="inlineStr">
         <is>
-          <t>UEB0007588</t>
+          <t>UEB0075887</t>
         </is>
       </c>
       <c r="C627" s="3" t="inlineStr">
@@ -24993,7 +24517,11 @@
           <t>53</t>
         </is>
       </c>
-      <c r="G628" s="3" t="inlineStr"/>
+      <c r="G628" s="3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="H628" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -25014,11 +24542,7 @@
           <t>Dhanaraj</t>
         </is>
       </c>
-      <c r="D629" s="3" t="inlineStr">
-        <is>
-          <t>Gurumani</t>
-        </is>
-      </c>
+      <c r="D629" s="3" t="inlineStr"/>
       <c r="E629" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -25034,7 +24558,11 @@
           <t>53</t>
         </is>
       </c>
-      <c r="H629" s="3" t="inlineStr"/>
+      <c r="H629" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="3" t="n">
@@ -25087,7 +24615,7 @@
       </c>
       <c r="C631" s="3" t="inlineStr">
         <is>
-          <t>PRADEEP KURUNG</t>
+          <t>BOPPI KUMARI</t>
         </is>
       </c>
       <c r="D631" s="3" t="inlineStr">
@@ -25140,7 +24668,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F632" s="3" t="inlineStr"/>
+      <c r="F632" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="G632" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -25176,11 +24708,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F633" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="F633" s="3" t="inlineStr"/>
       <c r="G633" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -25256,11 +24784,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F635" s="3" t="inlineStr">
-        <is>
-          <t>534</t>
-        </is>
-      </c>
+      <c r="F635" s="3" t="inlineStr"/>
       <c r="G635" s="3" t="inlineStr">
         <is>
           <t>58</t>
@@ -25283,7 +24807,7 @@
       </c>
       <c r="C636" s="3" t="inlineStr">
         <is>
-          <t>SAMBATH</t>
+          <t>MANIKANDAN</t>
         </is>
       </c>
       <c r="D636" s="3" t="inlineStr">
@@ -25336,7 +24860,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F637" s="3" t="inlineStr"/>
+      <c r="F637" s="3" t="inlineStr">
+        <is>
+          <t>534</t>
+        </is>
+      </c>
       <c r="G637" s="3" t="inlineStr">
         <is>
           <t>32</t>
@@ -25435,7 +24963,7 @@
       </c>
       <c r="C640" s="3" t="inlineStr">
         <is>
-          <t>Mathiash</t>
+          <t>Amalorpavamary</t>
         </is>
       </c>
       <c r="D640" s="3" t="inlineStr">
@@ -25478,11 +25006,7 @@
           <t>Edward Pranglin</t>
         </is>
       </c>
-      <c r="D641" s="3" t="inlineStr">
-        <is>
-          <t>Mathiash</t>
-        </is>
-      </c>
+      <c r="D641" s="3" t="inlineStr"/>
       <c r="E641" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -25510,12 +25034,12 @@
       </c>
       <c r="B642" s="3" t="inlineStr">
         <is>
-          <t>IPO0106112</t>
+          <t>IPD0106112</t>
         </is>
       </c>
       <c r="C642" s="3" t="inlineStr">
         <is>
-          <t>Arumugam</t>
+          <t>Rathinam</t>
         </is>
       </c>
       <c r="D642" s="3" t="inlineStr">
@@ -25555,7 +25079,7 @@
       </c>
       <c r="C643" s="3" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Arumugam</t>
         </is>
       </c>
       <c r="D643" s="3" t="inlineStr">
@@ -25595,24 +25119,20 @@
       </c>
       <c r="C644" s="3" t="inlineStr">
         <is>
+          <t>KAMALA</t>
+        </is>
+      </c>
+      <c r="D644" s="3" t="inlineStr">
+        <is>
           <t>KATHAVARAYAN</t>
         </is>
       </c>
-      <c r="D644" s="3" t="inlineStr">
-        <is>
-          <t>KATHAVARAYAN</t>
-        </is>
-      </c>
       <c r="E644" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
         </is>
       </c>
-      <c r="F644" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
+      <c r="F644" s="3" t="inlineStr"/>
       <c r="G644" s="3" t="inlineStr">
         <is>
           <t>44</t>
@@ -25630,7 +25150,7 @@
       </c>
       <c r="B645" s="3" t="inlineStr">
         <is>
-          <t>IPD0203430</t>
+          <t>IPD0020343</t>
         </is>
       </c>
       <c r="C645" s="3" t="inlineStr">
@@ -25670,12 +25190,12 @@
       </c>
       <c r="B646" s="3" t="inlineStr">
         <is>
-          <t>IPO0003561</t>
+          <t>IPO0035618</t>
         </is>
       </c>
       <c r="C646" s="3" t="inlineStr">
         <is>
-          <t>SAMYNATHAN</t>
+          <t>THANGARAJU</t>
         </is>
       </c>
       <c r="D646" s="3" t="inlineStr">
@@ -25750,7 +25270,7 @@
       </c>
       <c r="B648" s="3" t="inlineStr">
         <is>
-          <t>IPD0106138</t>
+          <t>IPO0106138</t>
         </is>
       </c>
       <c r="C648" s="3" t="inlineStr">
@@ -25773,11 +25293,7 @@
           <t>59</t>
         </is>
       </c>
-      <c r="G648" s="3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="G648" s="3" t="inlineStr"/>
       <c r="H648" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -25790,22 +25306,22 @@
       </c>
       <c r="B649" s="3" t="inlineStr">
         <is>
-          <t>GKY0561134</t>
+          <t>IPD0106195</t>
         </is>
       </c>
       <c r="C649" s="3" t="inlineStr">
         <is>
-          <t>RUTHRAMOORTHY</t>
+          <t>Thillaiparuvam</t>
         </is>
       </c>
       <c r="D649" s="3" t="inlineStr">
         <is>
-          <t>SINGAPERUMAL</t>
+          <t>Singaperumal</t>
         </is>
       </c>
       <c r="E649" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F649" s="3" t="inlineStr">
@@ -25813,14 +25329,10 @@
           <t>59</t>
         </is>
       </c>
-      <c r="G649" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="G649" s="3" t="inlineStr"/>
       <c r="H649" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -25830,22 +25342,22 @@
       </c>
       <c r="B650" s="3" t="inlineStr">
         <is>
-          <t>IPD0106195</t>
+          <t>GKY0561134</t>
         </is>
       </c>
       <c r="C650" s="3" t="inlineStr">
         <is>
-          <t>Thillaiparuvam</t>
+          <t>RUTHRAMOORTHY</t>
         </is>
       </c>
       <c r="D650" s="3" t="inlineStr">
         <is>
-          <t>Singaperumal</t>
+          <t>SINGAPERUMAL</t>
         </is>
       </c>
       <c r="E650" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F650" s="3" t="inlineStr">
@@ -25853,14 +25365,10 @@
           <t>59</t>
         </is>
       </c>
-      <c r="G650" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="G650" s="3" t="inlineStr"/>
       <c r="H650" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -25915,7 +25423,7 @@
       </c>
       <c r="C652" s="3" t="inlineStr">
         <is>
-          <t>Indhragandhi</t>
+          <t>Loganathan</t>
         </is>
       </c>
       <c r="D652" s="3" t="inlineStr">
@@ -25973,11 +25481,7 @@
           <t>61</t>
         </is>
       </c>
-      <c r="G653" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+      <c r="G653" s="3" t="inlineStr"/>
       <c r="H653" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -26074,11 +25578,7 @@
           <t>VIJAYALAKSHMI</t>
         </is>
       </c>
-      <c r="D656" s="3" t="inlineStr">
-        <is>
-          <t>CHEZHIAN</t>
-        </is>
-      </c>
+      <c r="D656" s="3" t="inlineStr"/>
       <c r="E656" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -26324,12 +25824,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F662" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="G662" s="3" t="inlineStr"/>
+      <c r="F662" s="3" t="inlineStr"/>
+      <c r="G662" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H662" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -26360,11 +25860,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F663" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="F663" s="3" t="inlineStr"/>
       <c r="G663" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -26387,7 +25883,7 @@
       </c>
       <c r="C664" s="3" t="inlineStr">
         <is>
-          <t>AZHAGUDHURAI</t>
+          <t>KABALI</t>
         </is>
       </c>
       <c r="D664" s="3" t="inlineStr">
@@ -26560,7 +26056,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F668" s="3" t="inlineStr"/>
+      <c r="F668" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="G668" s="3" t="inlineStr">
         <is>
           <t>45</t>
@@ -26596,11 +26096,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F669" s="3" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
+      <c r="F669" s="3" t="inlineStr"/>
       <c r="G669" s="3" t="inlineStr">
         <is>
           <t>39</t>
@@ -26623,7 +26119,7 @@
       </c>
       <c r="C670" s="3" t="inlineStr">
         <is>
-          <t>SADESHKUMARASAMY</t>
+          <t>JENISHA</t>
         </is>
       </c>
       <c r="D670" s="3" t="inlineStr">
@@ -26698,19 +26194,19 @@
       </c>
       <c r="B672" s="3" t="inlineStr">
         <is>
-          <t>IPD0069658</t>
+          <t>IPO0069658</t>
         </is>
       </c>
       <c r="C672" s="3" t="inlineStr">
         <is>
+          <t>VIDHYALAKSHMI</t>
+        </is>
+      </c>
+      <c r="D672" s="3" t="inlineStr">
+        <is>
           <t>GUNASEKARAN</t>
         </is>
       </c>
-      <c r="D672" s="3" t="inlineStr">
-        <is>
-          <t>GUNASEKARAN</t>
-        </is>
-      </c>
       <c r="E672" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -26726,11 +26222,7 @@
           <t>34</t>
         </is>
       </c>
-      <c r="H672" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H672" s="3" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="3" t="n">
@@ -26796,16 +26288,8 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F674" s="3" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G674" s="3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+      <c r="F674" s="3" t="inlineStr"/>
+      <c r="G674" s="3" t="inlineStr"/>
       <c r="H674" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -26863,7 +26347,7 @@
       </c>
       <c r="C676" s="3" t="inlineStr">
         <is>
-          <t>Banu</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="D676" s="3" t="inlineStr">
@@ -26881,11 +26365,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="G676" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
+      <c r="G676" s="3" t="inlineStr"/>
       <c r="H676" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -26898,7 +26378,7 @@
       </c>
       <c r="B677" s="3" t="inlineStr">
         <is>
-          <t>JTP0052166</t>
+          <t>JTP0521666</t>
         </is>
       </c>
       <c r="C677" s="3" t="inlineStr">
@@ -26978,22 +26458,22 @@
       </c>
       <c r="B679" s="3" t="inlineStr">
         <is>
-          <t>UIJ0020032</t>
+          <t>IPD0041038</t>
         </is>
       </c>
       <c r="C679" s="3" t="inlineStr">
         <is>
-          <t>AROKIARAJ</t>
+          <t>SUGANTHI</t>
         </is>
       </c>
       <c r="D679" s="3" t="inlineStr">
         <is>
-          <t>SAGAYARAJ</t>
+          <t>SELVARAJ</t>
         </is>
       </c>
       <c r="E679" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F679" s="3" t="inlineStr">
@@ -27001,14 +26481,10 @@
           <t>65</t>
         </is>
       </c>
-      <c r="G679" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="G679" s="3" t="inlineStr"/>
       <c r="H679" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -27018,22 +26494,22 @@
       </c>
       <c r="B680" s="3" t="inlineStr">
         <is>
-          <t>IPD0041038</t>
+          <t>ULJ0020032</t>
         </is>
       </c>
       <c r="C680" s="3" t="inlineStr">
         <is>
-          <t>SUGANTHI</t>
+          <t>AROKIARAJ</t>
         </is>
       </c>
       <c r="D680" s="3" t="inlineStr">
         <is>
-          <t>SELVARAJ</t>
+          <t>SAGAYARAJ</t>
         </is>
       </c>
       <c r="E680" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F680" s="3" t="inlineStr">
@@ -27048,7 +26524,7 @@
       </c>
       <c r="H680" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -27058,7 +26534,7 @@
       </c>
       <c r="B681" s="3" t="inlineStr">
         <is>
-          <t>UIJ0018895</t>
+          <t>ULJ0018895</t>
         </is>
       </c>
       <c r="C681" s="3" t="inlineStr">
@@ -27114,7 +26590,11 @@
         </is>
       </c>
       <c r="G682" s="3" t="inlineStr"/>
-      <c r="H682" s="3" t="inlineStr"/>
+      <c r="H682" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="3" t="n">
@@ -27130,18 +26610,22 @@
           <t>RATHINAVELU</t>
         </is>
       </c>
-      <c r="D683" s="3" t="inlineStr"/>
-      <c r="E683" s="3" t="inlineStr"/>
+      <c r="D683" s="3" t="inlineStr">
+        <is>
+          <t>RAVI</t>
+        </is>
+      </c>
+      <c r="E683" s="3" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
       <c r="F683" s="3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="G683" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="G683" s="3" t="inlineStr"/>
       <c r="H683" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -27164,7 +26648,7 @@
       </c>
       <c r="D684" s="3" t="inlineStr">
         <is>
-          <t>AROKIARAJ</t>
+          <t>AROKIARAS</t>
         </is>
       </c>
       <c r="E684" s="3" t="inlineStr">
@@ -27219,7 +26703,7 @@
       </c>
       <c r="G685" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H685" s="3" t="inlineStr">
@@ -27382,7 +26866,11 @@
           <t>53</t>
         </is>
       </c>
-      <c r="H689" s="3" t="inlineStr"/>
+      <c r="H689" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" s="3" t="n">
@@ -27450,7 +26938,7 @@
       </c>
       <c r="F691" s="3" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>717</t>
         </is>
       </c>
       <c r="G691" s="3" t="inlineStr">
@@ -27488,11 +26976,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F692" s="3" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="F692" s="3" t="inlineStr"/>
       <c r="G692" s="3" t="inlineStr"/>
       <c r="H692" s="3" t="inlineStr">
         <is>
@@ -27529,11 +27013,7 @@
           <t>71</t>
         </is>
       </c>
-      <c r="G693" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="G693" s="3" t="inlineStr"/>
       <c r="H693" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -27551,7 +27031,7 @@
       </c>
       <c r="C694" s="3" t="inlineStr">
         <is>
-          <t>BALAMURUGAN</t>
+          <t>REGA</t>
         </is>
       </c>
       <c r="D694" s="3" t="inlineStr">
@@ -27684,11 +27164,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F697" s="3" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+      <c r="F697" s="3" t="inlineStr"/>
       <c r="G697" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -27725,12 +27201,12 @@
         </is>
       </c>
       <c r="F698" s="3" t="inlineStr"/>
-      <c r="G698" s="3" t="inlineStr"/>
-      <c r="H698" s="3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+      <c r="G698" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H698" s="3" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="3" t="n">
@@ -27778,7 +27254,7 @@
       </c>
       <c r="B700" s="3" t="inlineStr">
         <is>
-          <t>IPO0211946</t>
+          <t>IPD0211946</t>
         </is>
       </c>
       <c r="C700" s="3" t="inlineStr"/>
@@ -27854,7 +27330,7 @@
       </c>
       <c r="B702" s="3" t="inlineStr">
         <is>
-          <t>IPO0063370</t>
+          <t>IPO0006337</t>
         </is>
       </c>
       <c r="C702" s="3" t="inlineStr">
@@ -27877,11 +27353,7 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G702" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="G702" s="3" t="inlineStr"/>
       <c r="H702" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -27952,12 +27424,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F704" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="G704" s="3" t="inlineStr"/>
+      <c r="F704" s="3" t="inlineStr"/>
+      <c r="G704" s="3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="H704" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -27970,7 +27442,7 @@
       </c>
       <c r="B705" s="3" t="inlineStr">
         <is>
-          <t>IPD0048660</t>
+          <t>IPD0648050</t>
         </is>
       </c>
       <c r="C705" s="3" t="inlineStr">
@@ -28015,7 +27487,7 @@
       </c>
       <c r="C706" s="3" t="inlineStr">
         <is>
-          <t>JAYALAKSHMI</t>
+          <t>MURUGAN</t>
         </is>
       </c>
       <c r="D706" s="3" t="inlineStr">
@@ -28055,7 +27527,7 @@
       </c>
       <c r="C707" s="3" t="inlineStr">
         <is>
-          <t>SANKARI</t>
+          <t>SANKAR</t>
         </is>
       </c>
       <c r="D707" s="3" t="inlineStr">
@@ -28108,11 +27580,7 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F708" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+      <c r="F708" s="3" t="inlineStr"/>
       <c r="G708" s="3" t="inlineStr">
         <is>
           <t>50</t>
@@ -28130,22 +27598,22 @@
       </c>
       <c r="B709" s="3" t="inlineStr">
         <is>
-          <t>JTP0486548</t>
+          <t>IPD0060269</t>
         </is>
       </c>
       <c r="C709" s="3" t="inlineStr">
         <is>
-          <t>MURUGAN</t>
+          <t>SUMATHI</t>
         </is>
       </c>
       <c r="D709" s="3" t="inlineStr">
         <is>
-          <t>RANGANATHAN</t>
+          <t>RAJENDRAN</t>
         </is>
       </c>
       <c r="E709" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F709" s="3" t="inlineStr">
@@ -28153,14 +27621,10 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G709" s="3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
+      <c r="G709" s="3" t="inlineStr"/>
       <c r="H709" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -28170,22 +27634,22 @@
       </c>
       <c r="B710" s="3" t="inlineStr">
         <is>
-          <t>IPD0060269</t>
+          <t>JTP0486548</t>
         </is>
       </c>
       <c r="C710" s="3" t="inlineStr">
         <is>
-          <t>SUMATHI</t>
+          <t>MURUGAN</t>
         </is>
       </c>
       <c r="D710" s="3" t="inlineStr">
         <is>
-          <t>RAJENDRAN</t>
+          <t>RANGANATHAN</t>
         </is>
       </c>
       <c r="E710" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F710" s="3" t="inlineStr">
@@ -28195,12 +27659,12 @@
       </c>
       <c r="G710" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H710" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -28309,11 +27773,7 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G713" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="G713" s="3" t="inlineStr"/>
       <c r="H713" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -28349,7 +27809,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G714" s="3" t="inlineStr"/>
+      <c r="G714" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H714" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -28425,11 +27889,7 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G716" s="3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+      <c r="G716" s="3" t="inlineStr"/>
       <c r="H716" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -28550,7 +28010,11 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H719" s="3" t="inlineStr"/>
+      <c r="H719" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" s="3" t="n">
@@ -28798,11 +28262,7 @@
           <t>Lalitha</t>
         </is>
       </c>
-      <c r="D726" s="3" t="inlineStr">
-        <is>
-          <t>Mani</t>
-        </is>
-      </c>
+      <c r="D726" s="3" t="inlineStr"/>
       <c r="E726" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
@@ -28848,7 +28308,11 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F727" s="3" t="inlineStr"/>
+      <c r="F727" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="G727" s="3" t="inlineStr">
         <is>
           <t>47</t>
@@ -28884,7 +28348,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F728" s="3" t="inlineStr"/>
+      <c r="F728" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="G728" s="3" t="inlineStr">
         <is>
           <t>44</t>
@@ -29130,11 +28598,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H734" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H734" s="3" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="3" t="n">
@@ -29227,14 +28691,14 @@
       </c>
       <c r="C737" s="3" t="inlineStr">
         <is>
+          <t>RAMU</t>
+        </is>
+      </c>
+      <c r="D737" s="3" t="inlineStr">
+        <is>
           <t>VINAYAGAM</t>
         </is>
       </c>
-      <c r="D737" s="3" t="inlineStr">
-        <is>
-          <t>VINAYAGAM</t>
-        </is>
-      </c>
       <c r="E737" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -29242,14 +28706,10 @@
       </c>
       <c r="F737" s="3" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="G737" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G737" s="3" t="inlineStr"/>
       <c r="H737" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -29302,17 +28762,17 @@
       </c>
       <c r="B739" s="3" t="inlineStr">
         <is>
-          <t>IPD0185702</t>
+          <t>XYA0838334</t>
         </is>
       </c>
       <c r="C739" s="3" t="inlineStr">
         <is>
-          <t>PRIYADHARSHINI</t>
+          <t>Pooniappan</t>
         </is>
       </c>
       <c r="D739" s="3" t="inlineStr">
         <is>
-          <t>RAMU</t>
+          <t>Panneersetvam</t>
         </is>
       </c>
       <c r="E739" s="3" t="inlineStr">
@@ -29327,12 +28787,12 @@
       </c>
       <c r="G739" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H739" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -29342,17 +28802,17 @@
       </c>
       <c r="B740" s="3" t="inlineStr">
         <is>
-          <t>XYA0838334</t>
+          <t>IPD0185702</t>
         </is>
       </c>
       <c r="C740" s="3" t="inlineStr">
         <is>
-          <t>Pooniappan</t>
+          <t>PRIYADHARSHINI</t>
         </is>
       </c>
       <c r="D740" s="3" t="inlineStr">
         <is>
-          <t>Panneerselvam</t>
+          <t>RAMU</t>
         </is>
       </c>
       <c r="E740" s="3" t="inlineStr">
@@ -29365,14 +28825,10 @@
           <t>80</t>
         </is>
       </c>
-      <c r="G740" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
+      <c r="G740" s="3" t="inlineStr"/>
       <c r="H740" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -29507,7 +28963,7 @@
       </c>
       <c r="C744" s="3" t="inlineStr">
         <is>
-          <t>KALAIVANY</t>
+          <t>ELUMALAI</t>
         </is>
       </c>
       <c r="D744" s="3" t="inlineStr">
@@ -29690,7 +29146,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="H748" s="3" t="inlineStr"/>
+      <c r="H748" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" s="3" t="n">
@@ -29718,7 +29178,7 @@
       </c>
       <c r="F749" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G749" s="3" t="inlineStr">
@@ -29761,11 +29221,7 @@
           <t>81</t>
         </is>
       </c>
-      <c r="G750" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="G750" s="3" t="inlineStr"/>
       <c r="H750" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -29841,7 +29297,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="G752" s="3" t="inlineStr"/>
+      <c r="G752" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="H752" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -29877,11 +29337,7 @@
           <t>81</t>
         </is>
       </c>
-      <c r="G753" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="G753" s="3" t="inlineStr"/>
       <c r="H753" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -30039,7 +29495,7 @@
       </c>
       <c r="G757" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H757" s="3" t="inlineStr">
@@ -30117,11 +29573,7 @@
           <t>82</t>
         </is>
       </c>
-      <c r="G759" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="G759" s="3" t="inlineStr"/>
       <c r="H759" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -30134,19 +29586,11 @@
       </c>
       <c r="B760" s="3" t="inlineStr">
         <is>
-          <t>IPO0003673</t>
-        </is>
-      </c>
-      <c r="C760" s="3" t="inlineStr">
-        <is>
-          <t>KANNAN</t>
-        </is>
-      </c>
-      <c r="D760" s="3" t="inlineStr">
-        <is>
-          <t>KANNAN</t>
-        </is>
-      </c>
+          <t>IPD0003673</t>
+        </is>
+      </c>
+      <c r="C760" s="3" t="inlineStr"/>
+      <c r="D760" s="3" t="inlineStr"/>
       <c r="E760" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -30194,7 +29638,7 @@
       </c>
       <c r="F761" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G761" s="3" t="inlineStr">
@@ -30234,7 +29678,7 @@
       </c>
       <c r="F762" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>62</t>
         </is>
       </c>
       <c r="G762" s="3" t="inlineStr">
@@ -30291,7 +29735,7 @@
       </c>
       <c r="C764" s="3" t="inlineStr">
         <is>
-          <t>KAKILA</t>
+          <t>KANNAN</t>
         </is>
       </c>
       <c r="D764" s="3" t="inlineStr">
@@ -30304,12 +29748,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F764" s="3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="G764" s="3" t="inlineStr"/>
+      <c r="F764" s="3" t="inlineStr"/>
+      <c r="G764" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H764" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -30367,7 +29811,7 @@
       </c>
       <c r="C766" s="3" t="inlineStr">
         <is>
-          <t>MOUROUVANE</t>
+          <t>KICHENIN</t>
         </is>
       </c>
       <c r="D766" s="3" t="inlineStr">
@@ -30422,7 +29866,7 @@
       </c>
       <c r="F767" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>63</t>
         </is>
       </c>
       <c r="G767" s="3" t="inlineStr">
@@ -30482,17 +29926,17 @@
       </c>
       <c r="B769" s="3" t="inlineStr">
         <is>
-          <t>IPD0003707</t>
+          <t>HJN0163139</t>
         </is>
       </c>
       <c r="C769" s="3" t="inlineStr">
         <is>
-          <t>Rajkumar</t>
+          <t>SADEESH KUMAR</t>
         </is>
       </c>
       <c r="D769" s="3" t="inlineStr">
         <is>
-          <t>Mahalingam</t>
+          <t>MAHALINGAM</t>
         </is>
       </c>
       <c r="E769" s="3" t="inlineStr">
@@ -30505,11 +29949,7 @@
           <t>83</t>
         </is>
       </c>
-      <c r="G769" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+      <c r="G769" s="3" t="inlineStr"/>
       <c r="H769" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -30522,17 +29962,17 @@
       </c>
       <c r="B770" s="3" t="inlineStr">
         <is>
-          <t>HJN0163139</t>
+          <t>IPD0003707</t>
         </is>
       </c>
       <c r="C770" s="3" t="inlineStr">
         <is>
-          <t>SADEESH KUMAR</t>
+          <t>Rajkumar</t>
         </is>
       </c>
       <c r="D770" s="3" t="inlineStr">
         <is>
-          <t>MAHALINGAM</t>
+          <t>Mahalingam</t>
         </is>
       </c>
       <c r="E770" s="3" t="inlineStr">
@@ -30545,12 +29985,12 @@
           <t>83</t>
         </is>
       </c>
-      <c r="G770" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H770" s="3" t="inlineStr"/>
+      <c r="G770" s="3" t="inlineStr"/>
+      <c r="H770" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" s="3" t="n">
@@ -30603,7 +30043,7 @@
       </c>
       <c r="C772" s="3" t="inlineStr">
         <is>
-          <t>NANDINI</t>
+          <t>MOUROUVANE</t>
         </is>
       </c>
       <c r="D772" s="3" t="inlineStr">
@@ -30622,7 +30062,11 @@
         </is>
       </c>
       <c r="G772" s="3" t="inlineStr"/>
-      <c r="H772" s="3" t="inlineStr"/>
+      <c r="H772" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="773">
       <c r="A773" s="3" t="n">
@@ -30710,7 +30154,7 @@
       </c>
       <c r="B775" s="3" t="inlineStr">
         <is>
-          <t>IPO0210005</t>
+          <t>IPD0210005</t>
         </is>
       </c>
       <c r="C775" s="3" t="inlineStr">
@@ -30718,7 +30162,11 @@
           <t>DILIP KUMAR</t>
         </is>
       </c>
-      <c r="D775" s="3" t="inlineStr"/>
+      <c r="D775" s="3" t="inlineStr">
+        <is>
+          <t>MAHALINGAM</t>
+        </is>
+      </c>
       <c r="E775" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -30806,7 +30254,7 @@
       </c>
       <c r="F777" s="3" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>834,</t>
         </is>
       </c>
       <c r="G777" s="3" t="inlineStr">
@@ -30814,7 +30262,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="H777" s="3" t="inlineStr"/>
+      <c r="H777" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" s="3" t="n">
@@ -30842,7 +30294,7 @@
       </c>
       <c r="F778" s="3" t="inlineStr">
         <is>
-          <t>83A</t>
+          <t>834</t>
         </is>
       </c>
       <c r="G778" s="3" t="inlineStr">
@@ -30882,7 +30334,7 @@
       </c>
       <c r="F779" s="3" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>634</t>
         </is>
       </c>
       <c r="G779" s="3" t="inlineStr">
@@ -31005,7 +30457,11 @@
           <t>84</t>
         </is>
       </c>
-      <c r="G782" s="3" t="inlineStr"/>
+      <c r="G782" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="H782" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -31063,7 +30519,7 @@
       </c>
       <c r="C784" s="3" t="inlineStr">
         <is>
-          <t>TAMILSELVAN</t>
+          <t>RADHIKA</t>
         </is>
       </c>
       <c r="D784" s="3" t="inlineStr">
@@ -31188,7 +30644,7 @@
       </c>
       <c r="D787" s="3" t="inlineStr">
         <is>
-          <t>Chinnadhurai</t>
+          <t>Chinnadhural</t>
         </is>
       </c>
       <c r="E787" s="3" t="inlineStr">
@@ -31236,7 +30692,11 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F788" s="3" t="inlineStr"/>
+      <c r="F788" s="3" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
       <c r="G788" s="3" t="inlineStr">
         <is>
           <t>47</t>
@@ -31354,7 +30814,7 @@
       </c>
       <c r="F791" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>85.</t>
         </is>
       </c>
       <c r="G791" s="3" t="inlineStr">
@@ -31374,7 +30834,7 @@
       </c>
       <c r="B792" s="3" t="inlineStr">
         <is>
-          <t>IPO0048553</t>
+          <t>IPD0048553</t>
         </is>
       </c>
       <c r="C792" s="3" t="inlineStr">
@@ -31477,11 +30937,7 @@
           <t>85</t>
         </is>
       </c>
-      <c r="G794" s="3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="G794" s="3" t="inlineStr"/>
       <c r="H794" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -31537,16 +30993,8 @@
           <t>IPD0040667</t>
         </is>
       </c>
-      <c r="C796" s="3" t="inlineStr">
-        <is>
-          <t>SRIDHARAN</t>
-        </is>
-      </c>
-      <c r="D796" s="3" t="inlineStr">
-        <is>
-          <t>RAVICHANDRAN</t>
-        </is>
-      </c>
+      <c r="C796" s="3" t="inlineStr"/>
+      <c r="D796" s="3" t="inlineStr"/>
       <c r="E796" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -31557,11 +31005,7 @@
           <t>85</t>
         </is>
       </c>
-      <c r="G796" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="G796" s="3" t="inlineStr"/>
       <c r="H796" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -31594,7 +31038,7 @@
       </c>
       <c r="F797" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>65</t>
         </is>
       </c>
       <c r="G797" s="3" t="inlineStr">
@@ -31654,37 +31098,37 @@
       </c>
       <c r="B799" s="3" t="inlineStr">
         <is>
-          <t>IPD0199950</t>
+          <t>IPD0185876</t>
         </is>
       </c>
       <c r="C799" s="3" t="inlineStr">
         <is>
-          <t>kishore</t>
+          <t>MAHALAKSHMI</t>
         </is>
       </c>
       <c r="D799" s="3" t="inlineStr">
         <is>
-          <t>sunitha</t>
+          <t>MAHESWARAN</t>
         </is>
       </c>
       <c r="E799" s="3" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F799" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>8S</t>
         </is>
       </c>
       <c r="G799" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H799" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -31694,22 +31138,22 @@
       </c>
       <c r="B800" s="3" t="inlineStr">
         <is>
-          <t>IPD0185876</t>
+          <t>IPD0199950</t>
         </is>
       </c>
       <c r="C800" s="3" t="inlineStr">
         <is>
-          <t>MAHALAKSHMI</t>
+          <t>kishore</t>
         </is>
       </c>
       <c r="D800" s="3" t="inlineStr">
         <is>
-          <t>MAHESWARAN</t>
+          <t>sunitha</t>
         </is>
       </c>
       <c r="E800" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Mother</t>
         </is>
       </c>
       <c r="F800" s="3" t="inlineStr">
@@ -31719,12 +31163,12 @@
       </c>
       <c r="G800" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H800" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -31739,10 +31183,14 @@
       </c>
       <c r="C801" s="3" t="inlineStr">
         <is>
-          <t>RAJI</t>
-        </is>
-      </c>
-      <c r="D801" s="3" t="inlineStr"/>
+          <t>EZHUMALAI</t>
+        </is>
+      </c>
+      <c r="D801" s="3" t="inlineStr">
+        <is>
+          <t>EZHUMALAI</t>
+        </is>
+      </c>
       <c r="E801" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -31798,7 +31246,11 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H802" s="3" t="inlineStr"/>
+      <c r="H802" s="3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="803">
       <c r="A803" s="3" t="n">
@@ -31829,11 +31281,7 @@
           <t>87</t>
         </is>
       </c>
-      <c r="G803" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="G803" s="3" t="inlineStr"/>
       <c r="H803" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -32094,12 +31542,7 @@
           <t>VAZHUMANI ALIAS RAJA</t>
         </is>
       </c>
-      <c r="D810" s="3" t="inlineStr">
-        <is>
-          <t>SUBRAMANIAN ALIAS
-PARASSURAMAN Photo</t>
-        </is>
-      </c>
+      <c r="D810" s="3" t="inlineStr"/>
       <c r="E810" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -32152,7 +31595,7 @@
       </c>
       <c r="G811" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H811" s="3" t="inlineStr">
@@ -32337,7 +31780,7 @@
       </c>
       <c r="D816" s="3" t="inlineStr">
         <is>
-          <t>Marimuthu</t>
+          <t>Manimuthu</t>
         </is>
       </c>
       <c r="E816" s="3" t="inlineStr">
@@ -32421,12 +31864,12 @@
           <t>Husband</t>
         </is>
       </c>
-      <c r="F818" s="3" t="inlineStr"/>
-      <c r="G818" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
+      <c r="F818" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G818" s="3" t="inlineStr"/>
       <c r="H818" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -32482,16 +31925,8 @@
           <t>IPO0106823</t>
         </is>
       </c>
-      <c r="C820" s="3" t="inlineStr">
-        <is>
-          <t>BRAMMACHARI</t>
-        </is>
-      </c>
-      <c r="D820" s="3" t="inlineStr">
-        <is>
-          <t>REDDEPPACHARI</t>
-        </is>
-      </c>
+      <c r="C820" s="3" t="inlineStr"/>
+      <c r="D820" s="3" t="inlineStr"/>
       <c r="E820" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -32519,12 +31954,12 @@
       </c>
       <c r="B821" s="3" t="inlineStr">
         <is>
-          <t>IPO0106831</t>
+          <t>IPD0106831</t>
         </is>
       </c>
       <c r="C821" s="3" t="inlineStr">
         <is>
-          <t>BRAMMACHARI</t>
+          <t>KALAVATHI</t>
         </is>
       </c>
       <c r="D821" s="3" t="inlineStr">
@@ -32719,16 +32154,8 @@
           <t>IPO0063289</t>
         </is>
       </c>
-      <c r="C826" s="3" t="inlineStr">
-        <is>
-          <t>SELVAM</t>
-        </is>
-      </c>
-      <c r="D826" s="3" t="inlineStr">
-        <is>
-          <t>KUPPUSAMY</t>
-        </is>
-      </c>
+      <c r="C826" s="3" t="inlineStr"/>
+      <c r="D826" s="3" t="inlineStr"/>
       <c r="E826" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -32756,7 +32183,7 @@
       </c>
       <c r="B827" s="3" t="inlineStr">
         <is>
-          <t>IPO0008852</t>
+          <t>IPO0088526</t>
         </is>
       </c>
       <c r="C827" s="3" t="inlineStr">
@@ -32836,37 +32263,37 @@
       </c>
       <c r="B829" s="3" t="inlineStr">
         <is>
-          <t>IPD0106849</t>
+          <t>IPD0003564</t>
         </is>
       </c>
       <c r="C829" s="3" t="inlineStr">
         <is>
-          <t>RAJESHWARI</t>
+          <t>LAKSHMIPATHY</t>
         </is>
       </c>
       <c r="D829" s="3" t="inlineStr">
         <is>
-          <t>GURUMANI</t>
+          <t>LAKSHMIPATHY</t>
         </is>
       </c>
       <c r="E829" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F829" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G829" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>39</t>
         </is>
       </c>
       <c r="H829" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -32876,37 +32303,33 @@
       </c>
       <c r="B830" s="3" t="inlineStr">
         <is>
-          <t>IPD0003566</t>
+          <t>IPD0106849</t>
         </is>
       </c>
       <c r="C830" s="3" t="inlineStr">
         <is>
-          <t>JOTHI</t>
+          <t>RAJESHWARI</t>
         </is>
       </c>
       <c r="D830" s="3" t="inlineStr">
         <is>
-          <t>LAKSHMIPATHY</t>
+          <t>GURUMANI</t>
         </is>
       </c>
       <c r="E830" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F830" s="3" t="inlineStr">
         <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G830" s="3" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G830" s="3" t="inlineStr"/>
       <c r="H830" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -32997,7 +32420,7 @@
       </c>
       <c r="C833" s="3" t="inlineStr">
         <is>
-          <t>ARIVOLI</t>
+          <t>DANARADJOU</t>
         </is>
       </c>
       <c r="D833" s="3" t="inlineStr">
@@ -33016,7 +32439,11 @@
         </is>
       </c>
       <c r="G833" s="3" t="inlineStr"/>
-      <c r="H833" s="3" t="inlineStr"/>
+      <c r="H833" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" s="3" t="n">
@@ -33045,7 +32472,7 @@
       </c>
       <c r="F834" s="3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>105,</t>
         </is>
       </c>
       <c r="G834" s="3" t="inlineStr">
@@ -33053,11 +32480,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="H834" s="3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
+      <c r="H834" s="3" t="inlineStr"/>
     </row>
     <row r="835">
       <c r="A835" s="3" t="n">
@@ -33145,7 +32568,7 @@
       </c>
       <c r="B837" s="3" t="inlineStr">
         <is>
-          <t>IPD0084673</t>
+          <t>IPO0084673</t>
         </is>
       </c>
       <c r="C837" s="3" t="inlineStr">
@@ -33253,7 +32676,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="H839" s="3" t="inlineStr"/>
+      <c r="H839" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="840">
       <c r="A840" s="3" t="n">
@@ -33309,7 +32736,11 @@
           <t>PRAKASH KUMAR</t>
         </is>
       </c>
-      <c r="D841" s="3" t="inlineStr"/>
+      <c r="D841" s="3" t="inlineStr">
+        <is>
+          <t>SHANMUGARAS</t>
+        </is>
+      </c>
       <c r="E841" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -33355,12 +32786,12 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F842" s="3" t="inlineStr"/>
-      <c r="G842" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="F842" s="3" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G842" s="3" t="inlineStr"/>
       <c r="H842" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -33378,7 +32809,7 @@
       </c>
       <c r="C843" s="3" t="inlineStr">
         <is>
-          <t>RICHARD</t>
+          <t>JOVAN</t>
         </is>
       </c>
       <c r="D843" s="3" t="inlineStr">
@@ -33418,7 +32849,7 @@
       </c>
       <c r="C844" s="3" t="inlineStr">
         <is>
-          <t>JOVAN</t>
+          <t>BREETLEE</t>
         </is>
       </c>
       <c r="D844" s="3" t="inlineStr">
@@ -33476,11 +32907,7 @@
           <t>110</t>
         </is>
       </c>
-      <c r="G845" s="3" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
+      <c r="G845" s="3" t="inlineStr"/>
       <c r="H845" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -33551,11 +32978,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F847" s="3" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
+      <c r="F847" s="3" t="inlineStr"/>
       <c r="G847" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -33591,7 +33014,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F848" s="3" t="inlineStr"/>
+      <c r="F848" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
       <c r="G848" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -33707,11 +33134,7 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F851" s="3" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
+      <c r="F851" s="3" t="inlineStr"/>
       <c r="G851" s="3" t="inlineStr">
         <is>
           <t>47</t>
@@ -33832,11 +33255,7 @@
           <t>111</t>
         </is>
       </c>
-      <c r="G854" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
+      <c r="G854" s="3" t="inlineStr"/>
       <c r="H854" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -33889,12 +33308,12 @@
       </c>
       <c r="B856" s="3" t="inlineStr">
         <is>
-          <t>UEB0047753</t>
+          <t>VEB0047753</t>
         </is>
       </c>
       <c r="C856" s="3" t="inlineStr">
         <is>
-          <t>PUSHPALATHA</t>
+          <t>RADHAKRISHNAN</t>
         </is>
       </c>
       <c r="D856" s="3" t="inlineStr">
@@ -33947,11 +33366,7 @@
           <t>Mother</t>
         </is>
       </c>
-      <c r="F857" s="3" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
+      <c r="F857" s="3" t="inlineStr"/>
       <c r="G857" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -34009,12 +33424,12 @@
       </c>
       <c r="B859" s="3" t="inlineStr">
         <is>
-          <t>IPD0048827</t>
+          <t>IPD0048751</t>
         </is>
       </c>
       <c r="C859" s="3" t="inlineStr">
         <is>
-          <t>THENNARASU</t>
+          <t>VASANTHA</t>
         </is>
       </c>
       <c r="D859" s="3" t="inlineStr">
@@ -34024,7 +33439,7 @@
       </c>
       <c r="E859" s="3" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="F859" s="3" t="inlineStr">
@@ -34045,22 +33460,18 @@
       </c>
       <c r="B860" s="3" t="inlineStr">
         <is>
-          <t>IPD0048751</t>
+          <t>IPD0048827</t>
         </is>
       </c>
       <c r="C860" s="3" t="inlineStr">
         <is>
-          <t>VASANTHA</t>
-        </is>
-      </c>
-      <c r="D860" s="3" t="inlineStr">
-        <is>
-          <t>KAMALAKANNAN</t>
-        </is>
-      </c>
+          <t>THENNARASU</t>
+        </is>
+      </c>
+      <c r="D860" s="3" t="inlineStr"/>
       <c r="E860" s="3" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="F860" s="3" t="inlineStr">
@@ -34068,11 +33479,7 @@
           <t>113</t>
         </is>
       </c>
-      <c r="G860" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="G860" s="3" t="inlineStr"/>
       <c r="H860" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -34148,11 +33555,7 @@
           <t>116</t>
         </is>
       </c>
-      <c r="G862" s="3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
+      <c r="G862" s="3" t="inlineStr"/>
       <c r="H862" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -34188,11 +33591,7 @@
           <t>116</t>
         </is>
       </c>
-      <c r="G863" s="3" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
+      <c r="G863" s="3" t="inlineStr"/>
       <c r="H863" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -34305,7 +33704,7 @@
       </c>
       <c r="F866" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>~</t>
         </is>
       </c>
       <c r="G866" s="3" t="inlineStr">
@@ -34345,7 +33744,7 @@
       </c>
       <c r="F867" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>=</t>
         </is>
       </c>
       <c r="G867" s="3" t="inlineStr">
@@ -34493,7 +33892,11 @@
           <t>VENDKADESAN</t>
         </is>
       </c>
-      <c r="D871" s="3" t="inlineStr"/>
+      <c r="D871" s="3" t="inlineStr">
+        <is>
+          <t>SUBRAMANAL</t>
+        </is>
+      </c>
       <c r="E871" s="3" t="inlineStr">
         <is>
           <t>Father</t>
@@ -34539,16 +33942,8 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F872" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G872" s="3" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
+      <c r="F872" s="3" t="inlineStr"/>
+      <c r="G872" s="3" t="inlineStr"/>
       <c r="H872" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -34606,7 +34001,7 @@
       </c>
       <c r="C874" s="3" t="inlineStr">
         <is>
-          <t>ViJl</t>
+          <t>ViJI</t>
         </is>
       </c>
       <c r="D874" s="3" t="inlineStr">
@@ -34721,7 +34116,7 @@
       </c>
       <c r="B877" s="3" t="inlineStr">
         <is>
-          <t>IPD0221432</t>
+          <t>IPO0221432</t>
         </is>
       </c>
       <c r="C877" s="3" t="inlineStr">
@@ -34767,7 +34162,7 @@
       </c>
       <c r="D878" s="3" t="inlineStr">
         <is>
-          <t>Packtyaraj</t>
+          <t>Packiyaraj</t>
         </is>
       </c>
       <c r="E878" s="3" t="inlineStr">
@@ -34775,7 +34170,11 @@
           <t>Father</t>
         </is>
       </c>
-      <c r="F878" s="3" t="inlineStr"/>
+      <c r="F878" s="3" t="inlineStr">
+        <is>
+          <t>No.18</t>
+        </is>
+      </c>
       <c r="G878" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -34813,7 +34212,7 @@
       </c>
       <c r="F879" s="3" t="inlineStr">
         <is>
-          <t>No, 23</t>
+          <t>No. 23</t>
         </is>
       </c>
       <c r="G879" s="3" t="inlineStr">
@@ -34870,24 +34269,20 @@
       </c>
       <c r="C881" s="3" t="inlineStr">
         <is>
+          <t>DHANALAKSHMI</t>
+        </is>
+      </c>
+      <c r="D881" s="3" t="inlineStr">
+        <is>
           <t>SAMYNATHAN</t>
         </is>
       </c>
-      <c r="D881" s="3" t="inlineStr">
-        <is>
-          <t>SAMYNATHAN</t>
-        </is>
-      </c>
       <c r="E881" s="3" t="inlineStr">
         <is>
           <t>Husband</t>
         </is>
       </c>
-      <c r="F881" s="3" t="inlineStr">
-        <is>
-          <t>NO.46</t>
-        </is>
-      </c>
+      <c r="F881" s="3" t="inlineStr"/>
       <c r="G881" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -34905,7 +34300,7 @@
       </c>
       <c r="B882" s="3" t="inlineStr">
         <is>
-          <t>IPD0022078</t>
+          <t>IPO0022078</t>
         </is>
       </c>
       <c r="C882" s="3" t="inlineStr">
@@ -35008,7 +34403,11 @@
           <t>no.81</t>
         </is>
       </c>
-      <c r="G884" s="3" t="inlineStr"/>
+      <c r="G884" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H884" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -35066,7 +34465,7 @@
       </c>
       <c r="C886" s="3" t="inlineStr">
         <is>
-          <t>MANJU</t>
+          <t>MANI</t>
         </is>
       </c>
       <c r="D886" s="3" t="inlineStr">
@@ -35101,7 +34500,7 @@
       </c>
       <c r="B887" s="3" t="inlineStr">
         <is>
-          <t>IPO0023008</t>
+          <t>IPO0230086</t>
         </is>
       </c>
       <c r="C887" s="3" t="inlineStr">
@@ -35141,7 +34540,7 @@
       </c>
       <c r="B888" s="3" t="inlineStr">
         <is>
-          <t>IPO0214965</t>
+          <t>IPO0021496</t>
         </is>
       </c>
       <c r="C888" s="3" t="inlineStr">
@@ -35181,17 +34580,17 @@
       </c>
       <c r="B889" s="3" t="inlineStr">
         <is>
-          <t>SOO3056124</t>
+          <t>KVY0454033</t>
         </is>
       </c>
       <c r="C889" s="3" t="inlineStr">
         <is>
-          <t>Fermine Shaly STANLEY</t>
+          <t>RAJA</t>
         </is>
       </c>
       <c r="D889" s="3" t="inlineStr">
         <is>
-          <t>STANLEY</t>
+          <t>THAMIZHANNAL</t>
         </is>
       </c>
       <c r="E889" s="3" t="inlineStr">
@@ -35201,13 +34600,13 @@
       </c>
       <c r="F889" s="3" t="inlineStr">
         <is>
-          <t>plot no. 3</t>
+          <t>Plot 33 4th cross</t>
         </is>
       </c>
       <c r="G889" s="3" t="inlineStr"/>
       <c r="H889" s="3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -35215,19 +34614,15 @@
       <c r="A890" s="3" t="n">
         <v>888</v>
       </c>
-      <c r="B890" s="3" t="inlineStr">
-        <is>
-          <t>KVY0454033</t>
-        </is>
-      </c>
+      <c r="B890" s="3" t="inlineStr"/>
       <c r="C890" s="3" t="inlineStr">
         <is>
-          <t>RAJA</t>
+          <t>Fermine Shaly STANLEY</t>
         </is>
       </c>
       <c r="D890" s="3" t="inlineStr">
         <is>
-          <t>THAMIZHANNAL</t>
+          <t>STANLEY</t>
         </is>
       </c>
       <c r="E890" s="3" t="inlineStr">
@@ -35237,71 +34632,19 @@
       </c>
       <c r="F890" s="3" t="inlineStr">
         <is>
-          <t>Plot 33 4th cross</t>
+          <t>plot no. 3</t>
         </is>
       </c>
       <c r="G890" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H890" s="3" t="inlineStr">
         <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="891">
-      <c r="A891" s="3" t="n">
-        <v>889</v>
-      </c>
-      <c r="B891" s="3" t="inlineStr">
-        <is>
-          <t>IPD0229732</t>
-        </is>
-      </c>
-      <c r="C891" s="3" t="inlineStr">
-        <is>
-          <t>KAMALUDIN</t>
-        </is>
-      </c>
-      <c r="D891" s="3" t="inlineStr">
-        <is>
-          <t>MOHAMMED CHERIEF</t>
-        </is>
-      </c>
-      <c r="E891" s="3" t="inlineStr">
-        <is>
-          <t>Father</t>
-        </is>
-      </c>
-      <c r="F891" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G891" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H891" s="3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="892">
-      <c r="A892" s="3" t="n">
-        <v>890</v>
-      </c>
-      <c r="B892" s="3" t="inlineStr"/>
-      <c r="C892" s="3" t="inlineStr"/>
-      <c r="D892" s="3" t="inlineStr"/>
-      <c r="E892" s="3" t="inlineStr"/>
-      <c r="F892" s="3" t="inlineStr"/>
-      <c r="G892" s="3" t="inlineStr"/>
-      <c r="H892" s="3" t="inlineStr"/>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/voter_output.xlsx
+++ b/output/voter_output.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H890"/>
+  <dimension ref="A1:H891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -672,7 +672,11 @@
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -789,7 +793,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -901,7 +909,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -1549,7 +1561,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -1585,7 +1601,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -1661,7 +1681,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -1697,7 +1721,11 @@
           <t>8A</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -2281,7 +2309,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -2505,7 +2537,11 @@
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -2861,7 +2897,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr"/>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3165,7 +3205,11 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr"/>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3197,7 +3241,11 @@
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr"/>
-      <c r="G73" s="3" t="inlineStr"/>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3313,7 +3361,11 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr"/>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3645,7 +3697,11 @@
           <t>18</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr"/>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3877,7 +3933,11 @@
           <t>19</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -3953,7 +4013,11 @@
           <t>194</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr"/>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -3989,7 +4053,11 @@
           <t>194</t>
         </is>
       </c>
-      <c r="G94" s="3" t="inlineStr"/>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -4265,7 +4333,11 @@
           <t>21</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr"/>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -4801,7 +4873,11 @@
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr"/>
-      <c r="G115" s="3" t="inlineStr"/>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -4989,7 +5065,11 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr"/>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -5497,7 +5577,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -5613,7 +5697,11 @@
           <t>No:2,Gayathri Homes,3rd</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr"/>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -5845,7 +5933,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr"/>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -6229,7 +6321,11 @@
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr"/>
-      <c r="G152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -6689,7 +6785,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G164" s="3" t="inlineStr"/>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -6845,7 +6945,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G168" s="3" t="inlineStr"/>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -6881,7 +6985,11 @@
           <t>1A</t>
         </is>
       </c>
-      <c r="G169" s="3" t="inlineStr"/>
+      <c r="G169" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -6917,7 +7025,11 @@
           <t>1A</t>
         </is>
       </c>
-      <c r="G170" s="3" t="inlineStr"/>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -7033,7 +7145,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr"/>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -7373,7 +7489,11 @@
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr"/>
-      <c r="G182" s="3" t="inlineStr"/>
+      <c r="G182" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8025,7 +8145,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="G199" s="3" t="inlineStr"/>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8061,7 +8185,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G200" s="3" t="inlineStr"/>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8177,7 +8305,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr"/>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -8514,7 +8646,11 @@
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr"/>
-      <c r="G212" s="3" t="inlineStr"/>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -8704,7 +8840,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
@@ -8962,7 +9098,11 @@
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr"/>
-      <c r="G224" s="3" t="inlineStr"/>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -9158,7 +9298,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="G229" s="3" t="inlineStr"/>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -9194,7 +9338,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="G230" s="3" t="inlineStr"/>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -9310,7 +9458,11 @@
           <t>7A 8A</t>
         </is>
       </c>
-      <c r="G233" s="3" t="inlineStr"/>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -9346,7 +9498,11 @@
           <t>7A 8A</t>
         </is>
       </c>
-      <c r="G234" s="3" t="inlineStr"/>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -9538,7 +9694,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="G239" s="3" t="inlineStr"/>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -9646,7 +9806,11 @@
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
-      <c r="G242" s="3" t="inlineStr"/>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -9754,7 +9918,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="G245" s="3" t="inlineStr"/>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H245" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10226,7 +10394,11 @@
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr"/>
-      <c r="G257" s="3" t="inlineStr"/>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10262,7 +10434,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="G258" s="3" t="inlineStr"/>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10298,7 +10474,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="G259" s="3" t="inlineStr"/>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10414,7 +10594,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="G262" s="3" t="inlineStr"/>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10806,7 +10990,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G272" s="3" t="inlineStr"/>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="H272" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -11034,7 +11222,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="G278" s="3" t="inlineStr"/>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="H278" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -11490,7 +11682,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="G290" s="3" t="inlineStr"/>
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="H290" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -11838,7 +12034,11 @@
           <t>14B</t>
         </is>
       </c>
-      <c r="G299" s="3" t="inlineStr"/>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="H299" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12186,7 +12386,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G308" s="3" t="inlineStr"/>
+      <c r="G308" s="3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="H308" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -12342,7 +12546,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G312" s="3" t="inlineStr"/>
+      <c r="G312" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H312" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12650,7 +12858,11 @@
           <t>15.</t>
         </is>
       </c>
-      <c r="G320" s="3" t="inlineStr"/>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="H320" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12726,7 +12938,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G322" s="3" t="inlineStr"/>
+      <c r="G322" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="H322" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12762,7 +12978,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="G323" s="3" t="inlineStr"/>
+      <c r="G323" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H323" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -13154,7 +13374,11 @@
           <t>15B</t>
         </is>
       </c>
-      <c r="G333" s="3" t="inlineStr"/>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H333" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -13386,7 +13610,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="G339" s="3" t="inlineStr"/>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="H339" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -13926,7 +14154,11 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G353" s="3" t="inlineStr"/>
+      <c r="G353" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="H353" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -14162,7 +14394,11 @@
           <t>17</t>
         </is>
       </c>
-      <c r="G359" s="3" t="inlineStr"/>
+      <c r="G359" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="H359" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -14754,7 +14990,11 @@
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
-      <c r="G374" s="3" t="inlineStr"/>
+      <c r="G374" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="H374" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -14982,7 +15222,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="G380" s="3" t="inlineStr"/>
+      <c r="G380" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="H380" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -15054,7 +15298,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="G382" s="3" t="inlineStr"/>
+      <c r="G382" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="H382" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -15090,7 +15338,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="G383" s="3" t="inlineStr"/>
+      <c r="G383" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="H383" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -15206,7 +15458,11 @@
           <t>20B.</t>
         </is>
       </c>
-      <c r="G386" s="3" t="inlineStr"/>
+      <c r="G386" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H386" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -16058,7 +16314,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="G408" s="3" t="inlineStr"/>
+      <c r="G408" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="H408" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -16366,7 +16626,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="G416" s="3" t="inlineStr"/>
+      <c r="G416" s="3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="H416" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -16598,7 +16862,11 @@
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
-      <c r="G422" s="3" t="inlineStr"/>
+      <c r="G422" s="3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="H422" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -16834,7 +17102,11 @@
           <t>25</t>
         </is>
       </c>
-      <c r="G428" s="3" t="inlineStr"/>
+      <c r="G428" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="H428" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -16942,7 +17214,11 @@
           <t>25,</t>
         </is>
       </c>
-      <c r="G431" s="3" t="inlineStr"/>
+      <c r="G431" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="H431" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17242,7 +17518,11 @@
           <t>27</t>
         </is>
       </c>
-      <c r="G439" s="3" t="inlineStr"/>
+      <c r="G439" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H439" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17278,7 +17558,11 @@
           <t>27</t>
         </is>
       </c>
-      <c r="G440" s="3" t="inlineStr"/>
+      <c r="G440" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="H440" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17354,7 +17638,11 @@
           <t>27</t>
         </is>
       </c>
-      <c r="G442" s="3" t="inlineStr"/>
+      <c r="G442" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="H442" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -17390,7 +17678,11 @@
           <t>27</t>
         </is>
       </c>
-      <c r="G443" s="3" t="inlineStr"/>
+      <c r="G443" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H443" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -17974,7 +18266,11 @@
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr"/>
-      <c r="G458" s="3" t="inlineStr"/>
+      <c r="G458" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H458" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -18210,7 +18506,11 @@
           <t>30</t>
         </is>
       </c>
-      <c r="G464" s="3" t="inlineStr"/>
+      <c r="G464" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="H464" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -18318,7 +18618,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="G467" s="3" t="inlineStr"/>
+      <c r="G467" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="H467" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -18354,7 +18658,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="G468" s="3" t="inlineStr"/>
+      <c r="G468" s="3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="H468" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -18510,7 +18818,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="G472" s="3" t="inlineStr"/>
+      <c r="G472" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="H472" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -18546,7 +18858,11 @@
           <t>31</t>
         </is>
       </c>
-      <c r="G473" s="3" t="inlineStr"/>
+      <c r="G473" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="H473" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -18890,7 +19206,11 @@
           <t>32</t>
         </is>
       </c>
-      <c r="G482" s="3" t="inlineStr"/>
+      <c r="G482" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="H482" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -18926,7 +19246,11 @@
           <t>33</t>
         </is>
       </c>
-      <c r="G483" s="3" t="inlineStr"/>
+      <c r="G483" s="3" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="H483" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -19118,7 +19442,11 @@
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr"/>
-      <c r="G488" s="3" t="inlineStr"/>
+      <c r="G488" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H488" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -19346,7 +19674,11 @@
         </is>
       </c>
       <c r="F494" s="3" t="inlineStr"/>
-      <c r="G494" s="3" t="inlineStr"/>
+      <c r="G494" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="H494" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -19582,7 +19914,11 @@
           <t>34</t>
         </is>
       </c>
-      <c r="G500" s="3" t="inlineStr"/>
+      <c r="G500" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H500" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -19658,7 +19994,11 @@
           <t>34</t>
         </is>
       </c>
-      <c r="G502" s="3" t="inlineStr"/>
+      <c r="G502" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="H502" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -19694,7 +20034,11 @@
           <t>34</t>
         </is>
       </c>
-      <c r="G503" s="3" t="inlineStr"/>
+      <c r="G503" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H503" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -20628,7 +20972,11 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G527" s="3" t="inlineStr"/>
+      <c r="G527" s="3" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="H527" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -20704,7 +21052,11 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G529" s="3" t="inlineStr"/>
+      <c r="G529" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="H529" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -20740,7 +21092,11 @@
           <t>36/52</t>
         </is>
       </c>
-      <c r="G530" s="3" t="inlineStr"/>
+      <c r="G530" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H530" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -20852,7 +21208,11 @@
           <t>37</t>
         </is>
       </c>
-      <c r="G533" s="3" t="inlineStr"/>
+      <c r="G533" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="H533" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21200,7 +21560,11 @@
           <t>38</t>
         </is>
       </c>
-      <c r="G542" s="3" t="inlineStr"/>
+      <c r="G542" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="H542" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -21660,7 +22024,11 @@
           <t>39B.</t>
         </is>
       </c>
-      <c r="G554" s="3" t="inlineStr"/>
+      <c r="G554" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="H554" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21816,7 +22184,11 @@
           <t>40</t>
         </is>
       </c>
-      <c r="G558" s="3" t="inlineStr"/>
+      <c r="G558" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="H558" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21892,7 +22264,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="G560" s="3" t="inlineStr"/>
+      <c r="G560" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H560" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -22004,7 +22380,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="G563" s="3" t="inlineStr"/>
+      <c r="G563" s="3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="H563" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22353,7 +22733,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="G572" s="3" t="inlineStr"/>
+      <c r="G572" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="H572" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -22381,7 +22765,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="G573" s="3" t="inlineStr"/>
+      <c r="G573" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="H573" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22805,7 +23193,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="G584" s="3" t="inlineStr"/>
+      <c r="G584" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="H584" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -23001,7 +23393,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="G589" s="3" t="inlineStr"/>
+      <c r="G589" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="H589" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -23157,7 +23553,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="G593" s="3" t="inlineStr"/>
+      <c r="G593" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="H593" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -23633,7 +24033,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="G605" s="3" t="inlineStr"/>
+      <c r="G605" s="3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
       <c r="H605" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -23789,7 +24193,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="G609" s="3" t="inlineStr"/>
+      <c r="G609" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H609" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -23897,7 +24305,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="G612" s="3" t="inlineStr"/>
+      <c r="G612" s="3" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="H612" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -24053,7 +24465,11 @@
           <t>49</t>
         </is>
       </c>
-      <c r="G616" s="3" t="inlineStr"/>
+      <c r="G616" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="H616" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -24129,7 +24545,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="G618" s="3" t="inlineStr"/>
+      <c r="G618" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="H618" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -24205,7 +24625,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="G620" s="3" t="inlineStr"/>
+      <c r="G620" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
       <c r="H620" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -24321,7 +24745,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="G623" s="3" t="inlineStr"/>
+      <c r="G623" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H623" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -25293,7 +25721,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="G648" s="3" t="inlineStr"/>
+      <c r="G648" s="3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="H648" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -25329,7 +25761,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="G649" s="3" t="inlineStr"/>
+      <c r="G649" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="H649" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -25365,7 +25801,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="G650" s="3" t="inlineStr"/>
+      <c r="G650" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="H650" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -25481,7 +25921,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="G653" s="3" t="inlineStr"/>
+      <c r="G653" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H653" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -26289,7 +26733,11 @@
         </is>
       </c>
       <c r="F674" s="3" t="inlineStr"/>
-      <c r="G674" s="3" t="inlineStr"/>
+      <c r="G674" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="H674" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -26365,7 +26813,11 @@
           <t>65</t>
         </is>
       </c>
-      <c r="G676" s="3" t="inlineStr"/>
+      <c r="G676" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
       <c r="H676" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -26481,7 +26933,11 @@
           <t>65</t>
         </is>
       </c>
-      <c r="G679" s="3" t="inlineStr"/>
+      <c r="G679" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H679" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -26589,7 +27045,11 @@
           <t>65,</t>
         </is>
       </c>
-      <c r="G682" s="3" t="inlineStr"/>
+      <c r="G682" s="3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="H682" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -26625,7 +27085,11 @@
           <t>65</t>
         </is>
       </c>
-      <c r="G683" s="3" t="inlineStr"/>
+      <c r="G683" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="H683" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -26977,7 +27441,11 @@
         </is>
       </c>
       <c r="F692" s="3" t="inlineStr"/>
-      <c r="G692" s="3" t="inlineStr"/>
+      <c r="G692" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="H692" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -27013,7 +27481,11 @@
           <t>71</t>
         </is>
       </c>
-      <c r="G693" s="3" t="inlineStr"/>
+      <c r="G693" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="H693" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -27353,7 +27825,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G702" s="3" t="inlineStr"/>
+      <c r="G702" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="H702" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -27621,7 +28097,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G709" s="3" t="inlineStr"/>
+      <c r="G709" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H709" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -27737,7 +28217,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G712" s="3" t="inlineStr"/>
+      <c r="G712" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="H712" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -27773,7 +28257,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G713" s="3" t="inlineStr"/>
+      <c r="G713" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H713" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -27889,7 +28377,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="G716" s="3" t="inlineStr"/>
+      <c r="G716" s="3" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
       <c r="H716" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -28125,7 +28617,11 @@
           <t>78</t>
         </is>
       </c>
-      <c r="G722" s="3" t="inlineStr"/>
+      <c r="G722" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="H722" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -28161,7 +28657,11 @@
           <t>78</t>
         </is>
       </c>
-      <c r="G723" s="3" t="inlineStr"/>
+      <c r="G723" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="H723" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -28709,7 +29209,11 @@
           <t>60</t>
         </is>
       </c>
-      <c r="G737" s="3" t="inlineStr"/>
+      <c r="G737" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="H737" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -28825,7 +29329,11 @@
           <t>80</t>
         </is>
       </c>
-      <c r="G740" s="3" t="inlineStr"/>
+      <c r="G740" s="3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="H740" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -29221,7 +29729,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="G750" s="3" t="inlineStr"/>
+      <c r="G750" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="H750" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -29337,7 +29849,11 @@
           <t>81</t>
         </is>
       </c>
-      <c r="G753" s="3" t="inlineStr"/>
+      <c r="G753" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="H753" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -29573,7 +30089,11 @@
           <t>82</t>
         </is>
       </c>
-      <c r="G759" s="3" t="inlineStr"/>
+      <c r="G759" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="H759" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -29949,7 +30469,11 @@
           <t>83</t>
         </is>
       </c>
-      <c r="G769" s="3" t="inlineStr"/>
+      <c r="G769" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="H769" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -29985,7 +30509,11 @@
           <t>83</t>
         </is>
       </c>
-      <c r="G770" s="3" t="inlineStr"/>
+      <c r="G770" s="3" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="H770" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -30061,7 +30589,11 @@
           <t>83</t>
         </is>
       </c>
-      <c r="G772" s="3" t="inlineStr"/>
+      <c r="G772" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H772" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -30937,7 +31469,11 @@
           <t>85</t>
         </is>
       </c>
-      <c r="G794" s="3" t="inlineStr"/>
+      <c r="G794" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="H794" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -31005,7 +31541,11 @@
           <t>85</t>
         </is>
       </c>
-      <c r="G796" s="3" t="inlineStr"/>
+      <c r="G796" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="H796" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -31281,7 +31821,11 @@
           <t>87</t>
         </is>
       </c>
-      <c r="G803" s="3" t="inlineStr"/>
+      <c r="G803" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="H803" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -31869,7 +32413,11 @@
           <t>95</t>
         </is>
       </c>
-      <c r="G818" s="3" t="inlineStr"/>
+      <c r="G818" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="H818" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -32098,7 +32646,11 @@
           <t>100</t>
         </is>
       </c>
-      <c r="G824" s="3" t="inlineStr"/>
+      <c r="G824" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="H824" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -32326,7 +32878,11 @@
           <t>103</t>
         </is>
       </c>
-      <c r="G830" s="3" t="inlineStr"/>
+      <c r="G830" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H830" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -32402,7 +32958,11 @@
           <t>103</t>
         </is>
       </c>
-      <c r="G832" s="3" t="inlineStr"/>
+      <c r="G832" s="3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="H832" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -32438,7 +32998,11 @@
           <t>103</t>
         </is>
       </c>
-      <c r="G833" s="3" t="inlineStr"/>
+      <c r="G833" s="3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="H833" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -32791,7 +33355,11 @@
           <t>107</t>
         </is>
       </c>
-      <c r="G842" s="3" t="inlineStr"/>
+      <c r="G842" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H842" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -32907,7 +33475,11 @@
           <t>110</t>
         </is>
       </c>
-      <c r="G845" s="3" t="inlineStr"/>
+      <c r="G845" s="3" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="H845" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -33255,7 +33827,11 @@
           <t>111</t>
         </is>
       </c>
-      <c r="G854" s="3" t="inlineStr"/>
+      <c r="G854" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
       <c r="H854" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -33447,7 +34023,11 @@
           <t>113</t>
         </is>
       </c>
-      <c r="G859" s="3" t="inlineStr"/>
+      <c r="G859" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="H859" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -33479,7 +34059,11 @@
           <t>113</t>
         </is>
       </c>
-      <c r="G860" s="3" t="inlineStr"/>
+      <c r="G860" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H860" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -33555,7 +34139,11 @@
           <t>116</t>
         </is>
       </c>
-      <c r="G862" s="3" t="inlineStr"/>
+      <c r="G862" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
       <c r="H862" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -33591,7 +34179,11 @@
           <t>116</t>
         </is>
       </c>
-      <c r="G863" s="3" t="inlineStr"/>
+      <c r="G863" s="3" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="H863" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -33943,7 +34535,11 @@
         </is>
       </c>
       <c r="F872" s="3" t="inlineStr"/>
-      <c r="G872" s="3" t="inlineStr"/>
+      <c r="G872" s="3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="H872" s="3" t="inlineStr">
         <is>
           <t>Female</t>
@@ -34603,7 +35199,11 @@
           <t>Plot 33 4th cross</t>
         </is>
       </c>
-      <c r="G889" s="3" t="inlineStr"/>
+      <c r="G889" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="H889" s="3" t="inlineStr">
         <is>
           <t>Male</t>
@@ -34643,6 +35243,46 @@
       <c r="H890" s="3" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="3" t="n">
+        <v>889</v>
+      </c>
+      <c r="B891" s="3" t="inlineStr">
+        <is>
+          <t>IPD0229732</t>
+        </is>
+      </c>
+      <c r="C891" s="3" t="inlineStr">
+        <is>
+          <t>KAMALUDIN</t>
+        </is>
+      </c>
+      <c r="D891" s="3" t="inlineStr">
+        <is>
+          <t>MOHAMMED CHERIEF</t>
+        </is>
+      </c>
+      <c r="E891" s="3" t="inlineStr">
+        <is>
+          <t>Father</t>
+        </is>
+      </c>
+      <c r="F891" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G891" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H891" s="3" t="inlineStr">
+        <is>
+          <t>Male</t>
         </is>
       </c>
     </row>
